--- a/tasks/HR_Troutly_T2_pto_liability_close/03_show_your_work.xlsx
+++ b/tasks/HR_Troutly_T2_pto_liability_close/03_show_your_work.xlsx
@@ -449,7 +449,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Biweekly accrual at the annual tier over 26, posted on the pay date; carryover capped at 40.0 hours at 06/30/2026; tiers by adjusted service date, the change in the period containing the anniversary; valued at the rate on file over 2080; ended employees out; wiki pages do not set policy.</t>
+          <t>Biweekly accrual at the annual tier over 26, posted on the pay date; carryover capped at 40.0 hours at 06/30/2026; tiers by adjusted service date, the change in the period containing the anniversary; valued at the rate on file over 2,080; ended employees out; wiki pages do not set policy.</t>
         </is>
       </c>
     </row>
@@ -500,7 +500,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>52 active employees. BambooHR carries 57 active rows: four contractors, three ended employees (03/20, 05/08 and 06/15/2026) and no row for TRT-0153 and TRT-0155, Never Loaded on the crosswalk.</t>
+          <t>52 active employees. BambooHR carries 57 active rows: four contractors, three employees whose employment ended 03/20, 05/08 and 06/15/2026, and no row for TRT-0153 and TRT-0155, Never Loaded on the crosswalk.</t>
         </is>
       </c>
     </row>
@@ -517,7 +517,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>51 balances at 06/30/2026; 11 above 40.0 hours, TRT-0005 at 92.50 the highest. The HRIS report, the load file and the July close carry them uncapped.</t>
+          <t>51 balances at 06/30/2026; eleven above 40.0 hours, TRT-0005 at 92.50 the highest. The HRIS report, the load file and the July close carry them uncapped.</t>
         </is>
       </c>
     </row>
@@ -534,7 +534,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Pay dates 07/10/2026, 07/24/2026, 08/07/2026, 08/21/2026 by 08/31/2026; 09/04/2026 is the fifth and is not posted.</t>
+          <t>Pay dates 07/10/2026, 07/24/2026, 08/07/2026 and 08/21/2026, posted by 08/31/2026; 09/04/2026 is the fifth and is not posted.</t>
         </is>
       </c>
     </row>
@@ -551,7 +551,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>9 migrated records read 07/01/2026 in BambooHR and on the roster and carry their true dates in the archive and the letters. TRT-0071 hired 03/08/2021, ended 08/25/2023, rehired 04/22/2024: a break under 365 days, bridged under handbook 7.6.</t>
+          <t>Nine migrated records read 07/01/2026 in BambooHR and on the roster and carry their true dates in the archive and the letters. TRT-0071 hired 03/08/2021, ended 08/25/2023, rehired 04/22/2024: a break under 365 days, bridged under handbook 7.6.</t>
         </is>
       </c>
     </row>
@@ -597,7 +597,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Historical offer letters, Marchetti, and handbook 5.4</t>
+          <t>Marchetti's offer letter in the historical letters and handbook 5.4</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -631,7 +631,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>The roster, the signed offers, /Recruiting/Offers/2026-07-02_Offer_TRT-0153_SIGNED.pdf and letter 13 of the historical letters, and Greenhouse</t>
+          <t>The roster, the signed offer /Recruiting/Offers/2026-07-02_Offer_TRT-0153_SIGNED.pdf, letter 13 of the historical letters and Greenhouse</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -687,7 +687,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>57 active rows, the loaded policies (6 wrong) and the loaded balances the run brings to the schedule.</t>
+          <t>57 active rows, the loaded policies, six of them wrong, and the loaded balances the run brings to the schedule.</t>
         </is>
       </c>
     </row>
@@ -743,7 +743,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>free</t>
+          <t>The page and its form</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>free</t>
+          <t>The page and its form</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -789,7 +789,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>free</t>
+          <t>The page and its form</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -812,7 +812,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>free</t>
+          <t>The page and its form</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -835,7 +835,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>determination</t>
+          <t>The determination</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -858,7 +858,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>determination</t>
+          <t>The determination</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -881,7 +881,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>determination</t>
+          <t>The determination</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -904,7 +904,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>determination</t>
+          <t>The determination</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -927,7 +927,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>determination</t>
+          <t>The determination</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -950,7 +950,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>determination</t>
+          <t>The determination</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -973,7 +973,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>determination</t>
+          <t>The determination</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -996,7 +996,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>determination</t>
+          <t>The determination</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>determination</t>
+          <t>The determination</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>determination</t>
+          <t>The determination</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>determination</t>
+          <t>The determination</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -1088,7 +1088,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>determination</t>
+          <t>The determination</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>determination</t>
+          <t>The determination</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>determination</t>
+          <t>The determination</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1157,7 +1157,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>bamboohr</t>
+          <t>BambooHR brought to the schedule</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1180,7 +1180,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>bamboohr</t>
+          <t>BambooHR brought to the schedule</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>bamboohr</t>
+          <t>BambooHR brought to the schedule</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1286,7 +1286,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>The archive's 06/30/2026 balance capped at 40.00; 11 capped; the two hires at 0.00.</t>
+          <t>The archive's 06/30/2026 balance capped at 40.00; eleven capped; the two hires at 0.00.</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>The rate on file over 2080 to four decimals: TRT-0088 at $118,000.00, TRT-0117 at $148,200.00 and TRT-0096 at $61,000.00 by the signed documents and the step.</t>
+          <t>The rate on file over 2,080 to four decimals: TRT-0088 at $118,000.00, TRT-0117 at $148,200.00 and TRT-0096 at $61,000.00 by the signed documents and the step.</t>
         </is>
       </c>
     </row>
@@ -1346,7 +1346,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Balance to two decimals, liability to the cent, the total the sum of the rounded rows: 1,522.17 hours and $92,739.54 ($92,772.88 under posted rounding).</t>
+          <t>Balance to two decimals, liability to the cent, the total the sum of the rounded rows: 1,522.17 hours and $92,739.54, $92,772.88 under posted rounding.</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>6 policies reassigned, 52 balances set, rows created for TRT-0153 and TRT-0155.</t>
+          <t>Six policies reassigned, 52 balances set, rows created for TRT-0153 and TRT-0155.</t>
         </is>
       </c>
     </row>
@@ -1546,17 +1546,17 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>215000.00</t>
+          <t>$215,000.00</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>103.3654</t>
+          <t>$103.3654</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2363.97</t>
+          <t>$2,363.97</t>
         </is>
       </c>
     </row>
@@ -1631,17 +1631,17 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>205000.00</t>
+          <t>$205,000.00</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>98.5577</t>
+          <t>$98.5577</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>6171.68</t>
+          <t>$6,171.68</t>
         </is>
       </c>
     </row>
@@ -1716,17 +1716,17 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>187510.00</t>
+          <t>$187,510.00</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>90.1490</t>
+          <t>$90.1490</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>5825.43</t>
+          <t>$5,825.43</t>
         </is>
       </c>
     </row>
@@ -1801,17 +1801,17 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>138700.00</t>
+          <t>$138,700.00</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>66.6827</t>
+          <t>$66.6827</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>4309.04</t>
+          <t>$4,309.04</t>
         </is>
       </c>
     </row>
@@ -1886,17 +1886,17 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>176400.00</t>
+          <t>$176,400.00</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>84.8077</t>
+          <t>$84.8077</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>1565.55</t>
+          <t>$1,565.55</t>
         </is>
       </c>
     </row>
@@ -1971,17 +1971,17 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>156700.00</t>
+          <t>$156,700.00</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>75.3365</t>
+          <t>$75.3365</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>4404.17</t>
+          <t>$4,404.17</t>
         </is>
       </c>
     </row>
@@ -2056,17 +2056,17 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>173300.00</t>
+          <t>$173,300.00</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>83.3173</t>
+          <t>$83.3173</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>4999.04</t>
+          <t>$4,999.04</t>
         </is>
       </c>
     </row>
@@ -2141,17 +2141,17 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>121300.00</t>
+          <t>$121,300.00</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>58.3173</t>
+          <t>$58.3173</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2476.15</t>
+          <t>$2,476.15</t>
         </is>
       </c>
     </row>
@@ -2226,17 +2226,17 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>154900.00</t>
+          <t>$154,900.00</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>74.4712</t>
+          <t>$74.4712</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>4353.59</t>
+          <t>$4,353.59</t>
         </is>
       </c>
     </row>
@@ -2311,17 +2311,17 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>157600.00</t>
+          <t>$157,600.00</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>75.7692</t>
+          <t>$75.7692</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2023.80</t>
+          <t>$2,023.80</t>
         </is>
       </c>
     </row>
@@ -2396,17 +2396,17 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>101400.00</t>
+          <t>$101,400.00</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>48.7500</t>
+          <t>$48.7500</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2459.93</t>
+          <t>$2,459.93</t>
         </is>
       </c>
     </row>
@@ -2481,17 +2481,17 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>161200.00</t>
+          <t>$161,200.00</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>77.5000</t>
+          <t>$77.5000</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2050.65</t>
+          <t>$2,050.65</t>
         </is>
       </c>
     </row>
@@ -2566,17 +2566,17 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>84600.00</t>
+          <t>$84,600.00</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>40.6731</t>
+          <t>$40.6731</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>1259.24</t>
+          <t>$1,259.24</t>
         </is>
       </c>
     </row>
@@ -2651,17 +2651,17 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>176400.00</t>
+          <t>$176,400.00</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>84.8077</t>
+          <t>$84.8077</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>4957.86</t>
+          <t>$4,957.86</t>
         </is>
       </c>
     </row>
@@ -2736,17 +2736,17 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>97350.00</t>
+          <t>$97,350.00</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>46.8029</t>
+          <t>$46.8029</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>1612.83</t>
+          <t>$1,612.83</t>
         </is>
       </c>
     </row>
@@ -2821,17 +2821,17 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>100800.00</t>
+          <t>$100,800.00</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>48.4615</t>
+          <t>$48.4615</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>385.75</t>
+          <t>$385.75</t>
         </is>
       </c>
     </row>
@@ -2906,17 +2906,17 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>132300.00</t>
+          <t>$132,300.00</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>63.6058</t>
+          <t>$63.6058</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>347.29</t>
+          <t>$347.29</t>
         </is>
       </c>
     </row>
@@ -2991,17 +2991,17 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>129800.00</t>
+          <t>$129,800.00</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>62.4038</t>
+          <t>$62.4038</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>418.73</t>
+          <t>$418.73</t>
         </is>
       </c>
     </row>
@@ -3076,17 +3076,17 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>103700.00</t>
+          <t>$103,700.00</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>49.8558</t>
+          <t>$49.8558</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>222.36</t>
+          <t>$222.36</t>
         </is>
       </c>
     </row>
@@ -3161,17 +3161,17 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>130450.00</t>
+          <t>$130,450.00</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>62.7163</t>
+          <t>$62.7163</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>1000.95</t>
+          <t>$1,000.95</t>
         </is>
       </c>
     </row>
@@ -3246,17 +3246,17 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>94750.00</t>
+          <t>$94,750.00</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>45.5529</t>
+          <t>$45.5529</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>1865.85</t>
+          <t>$1,865.85</t>
         </is>
       </c>
     </row>
@@ -3331,17 +3331,17 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>152600.00</t>
+          <t>$152,600.00</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>73.3654</t>
+          <t>$73.3654</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>1556.08</t>
+          <t>$1,556.08</t>
         </is>
       </c>
     </row>
@@ -3416,17 +3416,17 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>179800.00</t>
+          <t>$179,800.00</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>86.4423</t>
+          <t>$86.4423</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>2416.93</t>
+          <t>$2,416.93</t>
         </is>
       </c>
     </row>
@@ -3501,17 +3501,17 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>99300.00</t>
+          <t>$99,300.00</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>47.7404</t>
+          <t>$47.7404</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>2206.08</t>
+          <t>$2,206.08</t>
         </is>
       </c>
     </row>
@@ -3586,17 +3586,17 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>81000.00</t>
+          <t>$81,000.00</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>38.9423</t>
+          <t>$38.9423</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>2019.94</t>
+          <t>$2,019.94</t>
         </is>
       </c>
     </row>
@@ -3671,17 +3671,17 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>111800.00</t>
+          <t>$111,800.00</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>53.7500</t>
+          <t>$53.7500</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>2376.29</t>
+          <t>$2,376.29</t>
         </is>
       </c>
     </row>
@@ -3756,17 +3756,17 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>151900.00</t>
+          <t>$151,900.00</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>73.0288</t>
+          <t>$73.0288</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>2571.34</t>
+          <t>$2,571.34</t>
         </is>
       </c>
     </row>
@@ -3841,17 +3841,17 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>119600.00</t>
+          <t>$119,600.00</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>57.5000</t>
+          <t>$57.5000</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>1435.20</t>
+          <t>$1,435.20</t>
         </is>
       </c>
     </row>
@@ -3926,17 +3926,17 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>93100.00</t>
+          <t>$93,100.00</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>44.7596</t>
+          <t>$44.7596</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>837.45</t>
+          <t>$837.45</t>
         </is>
       </c>
     </row>
@@ -4011,17 +4011,17 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>63750.00</t>
+          <t>$63,750.00</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>30.6490</t>
+          <t>$30.6490</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>1592.52</t>
+          <t>$1,592.52</t>
         </is>
       </c>
     </row>
@@ -4096,17 +4096,17 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>118000.00</t>
+          <t>$118,000.00</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>56.7308</t>
+          <t>$56.7308</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>749.41</t>
+          <t>$749.41</t>
         </is>
       </c>
     </row>
@@ -4181,17 +4181,17 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>144500.00</t>
+          <t>$144,500.00</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>69.4712</t>
+          <t>$69.4712</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>1786.10</t>
+          <t>$1,786.10</t>
         </is>
       </c>
     </row>
@@ -4266,17 +4266,17 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>109300.00</t>
+          <t>$109,300.00</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>52.5481</t>
+          <t>$52.5481</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>1062.00</t>
+          <t>$1,062.00</t>
         </is>
       </c>
     </row>
@@ -4351,17 +4351,17 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>61000.00</t>
+          <t>$61,000.00</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>29.3269</t>
+          <t>$29.3269</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>602.96</t>
+          <t>$602.96</t>
         </is>
       </c>
     </row>
@@ -4436,17 +4436,17 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>77650.00</t>
+          <t>$77,650.00</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>37.3317</t>
+          <t>$37.3317</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>1383.51</t>
+          <t>$1,383.51</t>
         </is>
       </c>
     </row>
@@ -4521,17 +4521,17 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>108900.00</t>
+          <t>$108,900.00</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>52.3558</t>
+          <t>$52.3558</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>1272.77</t>
+          <t>$1,272.77</t>
         </is>
       </c>
     </row>
@@ -4606,17 +4606,17 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>109200.00</t>
+          <t>$109,200.00</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>52.5000</t>
+          <t>$52.5000</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>830.02</t>
+          <t>$830.02</t>
         </is>
       </c>
     </row>
@@ -4691,17 +4691,17 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>95850.00</t>
+          <t>$95,850.00</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>46.0817</t>
+          <t>$46.0817</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>1903.64</t>
+          <t>$1,903.64</t>
         </is>
       </c>
     </row>
@@ -4776,17 +4776,17 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>91200.00</t>
+          <t>$91,200.00</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>43.8462</t>
+          <t>$43.8462</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>1043.98</t>
+          <t>$1,043.98</t>
         </is>
       </c>
     </row>
@@ -4861,17 +4861,17 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>61900.00</t>
+          <t>$61,900.00</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>29.7596</t>
+          <t>$29.7596</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>790.41</t>
+          <t>$790.41</t>
         </is>
       </c>
     </row>
@@ -4946,17 +4946,17 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>148200.00</t>
+          <t>$148,200.00</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>71.2500</t>
+          <t>$71.2500</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>602.78</t>
+          <t>$602.78</t>
         </is>
       </c>
     </row>
@@ -5031,17 +5031,17 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>134000.00</t>
+          <t>$134,000.00</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>64.4231</t>
+          <t>$64.4231</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>1421.17</t>
+          <t>$1,421.17</t>
         </is>
       </c>
     </row>
@@ -5116,17 +5116,17 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>125600.00</t>
+          <t>$125,600.00</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>60.3846</t>
+          <t>$60.3846</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>1890.64</t>
+          <t>$1,890.64</t>
         </is>
       </c>
     </row>
@@ -5201,17 +5201,17 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>129750.00</t>
+          <t>$129,750.00</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>62.3798</t>
+          <t>$62.3798</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>1251.34</t>
+          <t>$1,251.34</t>
         </is>
       </c>
     </row>
@@ -5286,17 +5286,17 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>76850.00</t>
+          <t>$76,850.00</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>36.9471</t>
+          <t>$36.9471</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>159.24</t>
+          <t>$159.24</t>
         </is>
       </c>
     </row>
@@ -5371,17 +5371,17 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>94600.00</t>
+          <t>$94,600.00</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>45.4808</t>
+          <t>$45.4808</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>2242.66</t>
+          <t>$2,242.66</t>
         </is>
       </c>
     </row>
@@ -5456,17 +5456,17 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>47840.00</t>
+          <t>$47,840.00</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>23.0000</t>
+          <t>$23.0000</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>680.80</t>
+          <t>$680.80</t>
         </is>
       </c>
     </row>
@@ -5541,17 +5541,17 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>62450.00</t>
+          <t>$62,450.00</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>30.0240</t>
+          <t>$30.0240</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>369.60</t>
+          <t>$369.60</t>
         </is>
       </c>
     </row>
@@ -5626,17 +5626,17 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>92000.00</t>
+          <t>$92,000.00</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>44.2308</t>
+          <t>$44.2308</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>272.02</t>
+          <t>$272.02</t>
         </is>
       </c>
     </row>
@@ -5711,17 +5711,17 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>172500.00</t>
+          <t>$172,500.00</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>82.9327</t>
+          <t>$82.9327</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>255.43</t>
+          <t>$255.43</t>
         </is>
       </c>
     </row>
@@ -5796,17 +5796,17 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>56300.00</t>
+          <t>$56,300.00</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>27.0673</t>
+          <t>$27.0673</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>83.37</t>
+          <t>$83.37</t>
         </is>
       </c>
     </row>
@@ -5881,17 +5881,17 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>71900.00</t>
+          <t>$71,900.00</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>34.5673</t>
+          <t>$34.5673</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>$0.00</t>
         </is>
       </c>
     </row>
@@ -5914,7 +5914,7 @@
       <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
-          <t>1522.17</t>
+          <t>1,522.17</t>
         </is>
       </c>
       <c r="N54" t="inlineStr"/>
@@ -5922,7 +5922,7 @@
       <c r="P54" t="inlineStr"/>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>92739.54</t>
+          <t>$92,739.54</t>
         </is>
       </c>
     </row>

--- a/tasks/HR_Troutly_T2_pto_liability_close/03_show_your_work.xlsx
+++ b/tasks/HR_Troutly_T2_pto_liability_close/03_show_your_work.xlsx
@@ -1456,7 +1456,7 @@
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>Balance (posted rounding)</t>
+          <t>Balance, posted rounding</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">

--- a/tasks/HR_Troutly_T2_pto_liability_close/03_show_your_work.xlsx
+++ b/tasks/HR_Troutly_T2_pto_liability_close/03_show_your_work.xlsx
@@ -20,13 +20,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -49,8 +52,20 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -418,274 +433,279 @@
   </sheetPr>
   <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="110" customWidth="1" min="3" max="3"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Fact</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>The rules from 07/01/2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>PTO policy cutover memo of 06/20/2026, /HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>Biweekly accrual at the annual tier over 26, posted on the pay date; carryover capped at 40.0 hours at 06/30/2026; tiers by adjusted service date, the change in the period containing the anniversary; valued at the rate on file over 2,080; ended employees out; wiki pages do not set policy.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>What the handbook adds</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>Employee Handbook v3, /HR/Policies/Employee_Handbook_v3.pdf</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>Section 7 incorporates the memo; 2.2 part-time accrual pro-rata under 30 hours; 7.6 service bridges on a break under 365 days; 5.4 the $3,000.00 Support Specialist step; 3.2 the signed document over the record; 7.3 totals are the sum of the rounded rows.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>The superseded rules</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>PTO Policy 2025, /HR/Policies/PTO_Policy_2025.docx, and the Paid Time Off wiki page, /Wiki/Paid_Time_Off.md</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>Monthly accrual on the 1st and unlimited carryover, replaced 07/01/2026. The wiki page was last edited 01/2025.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>The current employees</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>Master employee roster of 08/31/2026, /HR/Data/2026-08-31_Master_Employee_Roster.xlsx, and the crosswalk of 08/28/2026, /HR/Data/2026-08-28_Employee_ID_Crosswalk.xlsx</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>52 active employees. BambooHR carries 57 active rows: four contractors, three employees whose employment ended 03/20, 05/08 and 06/15/2026, and no row for TRT-0153 and TRT-0155, Never Loaded on the crosswalk.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>The opening balances</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>SplinterHR final archive of 07/28/2026, Balances tab, /HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>51 balances at 06/30/2026; eleven above 40.0 hours, TRT-0005 at 92.50 the highest. The HRIS report, the load file and the July close carry them uncapped.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>The posted periods</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>Payroll procedures memo of 06/25/2026, /HR/Payroll/2026-06-25_Payroll_Procedures_Memo.docx</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>Pay dates 07/10/2026, 07/24/2026, 08/07/2026 and 08/21/2026, posted by 08/31/2026; 09/04/2026 is the fifth and is not posted.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>The service dates</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>The archive's Employees tab and the historical offer letters, /HR/People/Offer_Letters/Historical_Offer_Letters_2020-2026.pdf</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>Nine migrated records read 07/01/2026 in BambooHR and on the roster and carry their true dates in the archive and the letters. TRT-0071 hired 03/08/2021, ended 08/25/2023, rehired 04/22/2024: a break under 365 days, bridged under handbook 7.6.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>The tier change in the window</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>The archive's dates and the memo's timing rule</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>TRT-0018 reaches five years inside the fourth period: three periods at 120 and one at 160, 20.0000 hours accrued.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>The signed pay changes</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>Promotion approval TRT-0088 of 06/10/2026, /HR/Comp/Promotions/2026-06-10_Promotion_Approval_TRT-0088.docx, and comp amendment TRT-0117 of 05/12/2026, /HR/Comp/Amendments/2026-05-12_Comp_Amendment_TRT-0117.pdf</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>$118,000.00 from 06/16/2026 and $148,200.00 from 05/16/2026, signed. BambooHR, the roster and payroll carry the loaded rates.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>The step</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>Marchetti's offer letter in the historical letters and handbook 5.4</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>TRT-0096 steps $3,000.00 on her 08/17/2026 anniversary: $61,000.00 on file at 08/31/2026.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>The part-time schedule</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>Schedule change form TRT-0141 of 08/10/2026, /HR/Benefits/2026-08-10_Schedule_Change_TRT-0141.pdf</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>25 hours to 32 hours effective 08/10/2026; pro-rata under 30 hours, so three periods at 25 and one at 32.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>The two unloaded hires</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>The roster, the signed offer /Recruiting/Offers/2026-07-02_Offer_TRT-0153_SIGNED.pdf, letter 13 of the historical letters and Greenhouse</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>Okonkwo started 07/22/2026 at $92,000.00, moved from 07/13/2026 by the thread of 07/09/2026; Ibarra 08/03/2026 at $56,300.00. Both accrue at 80 from the period containing the start, as BambooHR credited TRT-0150: 6.15 and 3.08 hours.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>Approved time off</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>BambooHR TimeOffRequest</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>24 approved requests, 560.00 hours, all in July; TRT-0001 40.00 hours.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>The July close</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>/Finance/Close/2026-07_Close_Package.xlsx</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>The requester's method: the HRIS balance, tier and rate per row, three ended employees inside, $90,862.13 booked.</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>The BambooHR tables</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>Employee, EmployeePolicy, TimeOffBalance, TimeOffPolicy</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>57 active rows, the loaded policies, six of them wrong, and the loaded balances the run brings to the schedule.</t>
         </is>
@@ -704,529 +724,545 @@
   </sheetPr>
   <dimension ref="A1:E24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="110" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Verifier</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Family</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Weight</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Gate</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
+      <c r="A2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>States that a Wiki.js page titled PTO Liability - 08/31/2026 is published.</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>The page and its form</t>
         </is>
       </c>
-      <c r="D2" t="n">
+      <c r="D2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
+      <c r="A3" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>States, on the PTO liability page, the 52 current employees at 08/31/2026 as the only employee rows.</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>The page and its form</t>
         </is>
       </c>
-      <c r="D3" t="n">
+      <c r="D3" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
+      <c r="A4" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>States, on the PTO liability page, hours to two decimals, hourly rates to four decimals, dollars to the cent and a total equal to the sum of the rows.</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>The page and its form</t>
         </is>
       </c>
-      <c r="D4" t="n">
+      <c r="D4" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
+      <c r="A5" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>States, on the PTO liability page, a summary with the employee count, the total hours and the total dollar liability.</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>The page and its form</t>
         </is>
       </c>
-      <c r="D5" t="n">
+      <c r="D5" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
+      <c r="A6" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>States, on the PTO liability page, a total dollar liability of $92,739.54.</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>The determination</t>
         </is>
       </c>
-      <c r="D6" t="n">
+      <c r="D6" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Critical value</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
+      <c r="A7" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>States, on the PTO liability page, an opening balance of 40.00 hours for each of the 11 employees whose 06/30/2026 balance exceeded 40.0 hours.</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>The determination</t>
         </is>
       </c>
-      <c r="D7" t="n">
+      <c r="D7" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="n">
+      <c r="A8" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>States, on the PTO liability page, the 120-hour tier for TRT-0043, TRT-0051, TRT-0058, TRT-0079 and TRT-0083.</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>The determination</t>
         </is>
       </c>
-      <c r="D8" t="n">
+      <c r="D8" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="n">
+      <c r="A9" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>States, on the PTO liability page, the 160-hour tier for Samuel Burkenham, TRT-0071, with service bridged to 03/08/2021.</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>The determination</t>
         </is>
       </c>
-      <c r="D9" t="n">
+      <c r="D9" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="n">
+      <c r="A10" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>States, on the PTO liability page, an accrual of 20.0000 hours for Marisela Thornbury, TRT-0018, three periods at the 120-hour tier and one at 160.</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>The determination</t>
         </is>
       </c>
-      <c r="D10" t="n">
+      <c r="D10" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="n">
+      <c r="A11" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>States, on the PTO liability page, an hourly rate of $56.7308 for Yolanda Featherstone, TRT-0088.</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>The determination</t>
         </is>
       </c>
-      <c r="D11" t="n">
+      <c r="D11" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="n">
+      <c r="A12" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>States, on the PTO liability page, an hourly rate of $71.2500 for Belaviv Luk, TRT-0117.</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>The determination</t>
         </is>
       </c>
-      <c r="D12" t="n">
+      <c r="D12" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="n">
+      <c r="A13" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>States, on the PTO liability page, an hourly rate of $29.3269 for Delphine Marchetti, TRT-0096.</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>The determination</t>
         </is>
       </c>
-      <c r="D13" t="n">
+      <c r="D13" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="n">
+      <c r="A14" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>States, on the PTO liability page, a balance of 29.60 hours for Beatriz Quintanilla, TRT-0141.</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>The determination</t>
         </is>
       </c>
-      <c r="D14" t="n">
+      <c r="D14" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="n">
+      <c r="A15" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>States, on the PTO liability page, no contractor row, CTR-2001 to CTR-2004.</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>The determination</t>
         </is>
       </c>
-      <c r="D15" t="n">
+      <c r="D15" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="n">
+      <c r="A16" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>States, on the PTO liability page, no row for TRT-0037, TRT-0049, TRT-0064 or TRT-0006.</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>The determination</t>
         </is>
       </c>
-      <c r="D16" t="n">
+      <c r="D16" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="n">
+      <c r="A17" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>States, on the PTO liability page, Simone Okonkwo, TRT-0153, and Rafael Ibarra, TRT-0155, at the 80-hour tier with accruals since their start dates.</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>The determination</t>
         </is>
       </c>
-      <c r="D17" t="n">
+      <c r="D17" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="n">
+      <c r="A18" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>States, on the PTO liability page, a balance of 62.62 hours for Sora Jackson, TRT-0002, four posted periods at the 160-hour tier.</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>The determination</t>
         </is>
       </c>
-      <c r="D18" t="n">
+      <c r="D18" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="n">
+      <c r="A19" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>States, on the PTO liability page, a balance of 22.87 hours for Michael Labeson, TRT-0001, with 40.00 hours of approved time off deducted.</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
         <is>
           <t>The determination</t>
         </is>
       </c>
-      <c r="D19" t="n">
+      <c r="D19" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="n">
+      <c r="A20" s="2" t="n">
         <v>19</v>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>States, in BambooHR, the PTO policy the schedule's tier gives for each of the 6 employees whose loaded policy differed.</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>BambooHR brought to the schedule</t>
         </is>
       </c>
-      <c r="D20" t="n">
+      <c r="D20" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="n">
+      <c r="A21" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>States, in BambooHR, a PTO balance equal to the schedule's 08/31/2026 balance for every employee on the schedule.</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
         <is>
           <t>BambooHR brought to the schedule</t>
         </is>
       </c>
-      <c r="D21" t="n">
+      <c r="D21" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="n">
+      <c r="A22" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>States, in BambooHR, a PTO balance row for TRT-0153 and TRT-0155.</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
         <is>
           <t>BambooHR brought to the schedule</t>
         </is>
       </c>
-      <c r="D22" t="n">
+      <c r="D22" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
-    <row r="23"/>
+    <row r="23">
+      <c r="A23" s="2" t="n"/>
+      <c r="B23" s="2" t="n"/>
+      <c r="C23" s="2" t="n"/>
+      <c r="D23" s="2" t="n"/>
+      <c r="E23" s="2" t="n"/>
+    </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>The determination carries 75 of 92 points; the gate is the total. Every row is read from the Wiki.js pages table or the BambooHR tables.</t>
         </is>
       </c>
+      <c r="C24" s="2" t="n"/>
+      <c r="D24" s="2" t="n"/>
+      <c r="E24" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1241,134 +1277,138 @@
   </sheetPr>
   <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="120" customWidth="1" min="2" max="2"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Step</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Result</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>The population</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>52 from the roster and the org chart: BambooHR's 57 active less four contractors less three ended plus the two unloaded hires.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>The rules</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>The cutover memo over the 2025 policy and the wiki page; the handbook's bridging, part-time, step and signed-document rules.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>The opening balances</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>The archive's 06/30/2026 balance capped at 40.00; eleven capped; the two hires at 0.00.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>The service dates and tiers</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>The archive's and the letters' dates over the loaded 07/01/2026; TRT-0071 bridged to 03/08/2021 at 160; five migrated records at 120; TRT-0018 to 160 in the fourth period.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>The accruals</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>Four posted periods at the tier over 26 to four decimals, the period containing a start credited in full; TRT-0141 pro-rata at 25 then 32 hours.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>The usage</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>560.00 approved hours deducted, 40.00 on TRT-0001.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>The rates</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>The rate on file over 2,080 to four decimals: TRT-0088 at $118,000.00, TRT-0117 at $148,200.00 and TRT-0096 at $61,000.00 by the signed documents and the step.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>The rows and the totals</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>Balance to two decimals, liability to the cent, the total the sum of the rounded rows: 1,522.17 hours and $92,739.54, $92,772.88 under posted rounding.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>The page</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>PTO Liability - 08/31/2026: the summary above the table, seven columns, 52 rows keyed by ID, published.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>BambooHR</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>Six policies reassigned, 52 balances set, rows created for TRT-0153 and TRT-0155.</t>
         </is>
@@ -1387,4540 +1427,4559 @@
   </sheetPr>
   <dimension ref="A1:Q54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="6" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="8" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>Employee ID</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>Department</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>Adjusted service date</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Tier</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>Opening 06/30/2026</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>Opening capped</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="3" t="inlineStr">
         <is>
           <t>Accrual p1</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="3" t="inlineStr">
         <is>
           <t>Accrual p2</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="3" t="inlineStr">
         <is>
           <t>Accrual p3</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="3" t="inlineStr">
         <is>
           <t>Accrual p4</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="3" t="inlineStr">
         <is>
           <t>Used</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="3" t="inlineStr">
         <is>
           <t>Balance 08/31/2026</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="3" t="inlineStr">
         <is>
           <t>Balance, posted rounding</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="3" t="inlineStr">
         <is>
           <t>Annual rate</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="3" t="inlineStr">
         <is>
           <t>Hourly rate</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="3" t="inlineStr">
         <is>
           <t>Liability</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>TRT-0001</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>Michael Labeson</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>Finance and Corporate</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>03/04/2019</t>
         </is>
       </c>
-      <c r="E2" t="n">
+      <c r="E2" s="4" t="n">
         <v>160</v>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="4" t="inlineStr">
         <is>
           <t>38.25</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>38.25</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H2" s="4" t="inlineStr">
         <is>
           <t>6.1538</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I2" s="4" t="inlineStr">
         <is>
           <t>6.1538</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J2" s="4" t="inlineStr">
         <is>
           <t>6.1538</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K2" s="4" t="inlineStr">
         <is>
           <t>6.1538</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="L2" s="4" t="inlineStr">
         <is>
           <t>40.00</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="M2" s="4" t="inlineStr">
         <is>
           <t>22.87</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="N2" s="4" t="inlineStr">
         <is>
           <t>22.85</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="O2" s="4" t="inlineStr">
         <is>
           <t>$215,000.00</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="P2" s="4" t="inlineStr">
         <is>
           <t>$103.3654</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Q2" s="4" t="inlineStr">
         <is>
           <t>$2,363.97</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>TRT-0002</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>Sora Jackson</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>Engineering</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>03/04/2019</t>
         </is>
       </c>
-      <c r="E3" t="n">
+      <c r="E3" s="4" t="n">
         <v>160</v>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>38.00</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>38.00</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>6.1538</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I3" s="4" t="inlineStr">
         <is>
           <t>6.1538</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J3" s="4" t="inlineStr">
         <is>
           <t>6.1538</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="K3" s="4" t="inlineStr">
         <is>
           <t>6.1538</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="L3" s="4" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="M3" s="4" t="inlineStr">
         <is>
           <t>62.62</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="N3" s="4" t="inlineStr">
         <is>
           <t>62.60</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="O3" s="4" t="inlineStr">
         <is>
           <t>$205,000.00</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="P3" s="4" t="inlineStr">
         <is>
           <t>$98.5577</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="Q3" s="4" t="inlineStr">
         <is>
           <t>$6,171.68</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>TRT-0005</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>Mikelle Hosana</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>Engineering</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>05/20/2019</t>
         </is>
       </c>
-      <c r="E4" t="n">
+      <c r="E4" s="4" t="n">
         <v>160</v>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>92.50</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>40.00</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H4" s="4" t="inlineStr">
         <is>
           <t>6.1538</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="I4" s="4" t="inlineStr">
         <is>
           <t>6.1538</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J4" s="4" t="inlineStr">
         <is>
           <t>6.1538</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="K4" s="4" t="inlineStr">
         <is>
           <t>6.1538</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="L4" s="4" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="M4" s="4" t="inlineStr">
         <is>
           <t>64.62</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="N4" s="4" t="inlineStr">
         <is>
           <t>64.60</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="O4" s="4" t="inlineStr">
         <is>
           <t>$187,510.00</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="P4" s="4" t="inlineStr">
         <is>
           <t>$90.1490</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="Q4" s="4" t="inlineStr">
         <is>
           <t>$5,825.43</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>TRT-0009</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>Krystale Jumawan</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>Finance and Corporate</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>06/14/2021</t>
         </is>
       </c>
-      <c r="E5" t="n">
+      <c r="E5" s="4" t="n">
         <v>160</v>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>84.00</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>40.00</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>6.1538</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I5" s="4" t="inlineStr">
         <is>
           <t>6.1538</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J5" s="4" t="inlineStr">
         <is>
           <t>6.1538</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="K5" s="4" t="inlineStr">
         <is>
           <t>6.1538</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="L5" s="4" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="M5" s="4" t="inlineStr">
         <is>
           <t>64.62</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="N5" s="4" t="inlineStr">
         <is>
           <t>64.60</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="O5" s="4" t="inlineStr">
         <is>
           <t>$138,700.00</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="P5" s="4" t="inlineStr">
         <is>
           <t>$66.6827</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="Q5" s="4" t="inlineStr">
         <is>
           <t>$4,309.04</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>TRT-0012</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>Jessica Ko</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>Engineering</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>09/13/2021</t>
         </is>
       </c>
-      <c r="E6" t="n">
+      <c r="E6" s="4" t="n">
         <v>120</v>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F6" s="4" t="inlineStr">
         <is>
           <t>71.50</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G6" s="4" t="inlineStr">
         <is>
           <t>40.00</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>4.6154</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>4.6154</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>4.6154</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>4.6154</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>4.6154</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>4.6154</t>
+        </is>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>4.6154</t>
+        </is>
+      </c>
+      <c r="K6" s="4" t="inlineStr">
+        <is>
+          <t>4.6154</t>
+        </is>
+      </c>
+      <c r="L6" s="4" t="inlineStr">
         <is>
           <t>40.00</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="M6" s="4" t="inlineStr">
         <is>
           <t>18.46</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="N6" s="4" t="inlineStr">
         <is>
           <t>18.48</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="O6" s="4" t="inlineStr">
         <is>
           <t>$176,400.00</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="P6" s="4" t="inlineStr">
         <is>
           <t>$84.8077</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="Q6" s="4" t="inlineStr">
         <is>
           <t>$1,565.55</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>TRT-0014</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>Rohan Iyer</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>Engineering</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>10/04/2021</t>
         </is>
       </c>
-      <c r="E7" t="n">
+      <c r="E7" s="4" t="n">
         <v>120</v>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>66.00</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>40.00</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>4.6154</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>4.6154</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>4.6154</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>4.6154</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>4.6154</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>4.6154</t>
+        </is>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>4.6154</t>
+        </is>
+      </c>
+      <c r="K7" s="4" t="inlineStr">
+        <is>
+          <t>4.6154</t>
+        </is>
+      </c>
+      <c r="L7" s="4" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="M7" s="4" t="inlineStr">
         <is>
           <t>58.46</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="N7" s="4" t="inlineStr">
         <is>
           <t>58.48</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="O7" s="4" t="inlineStr">
         <is>
           <t>$156,700.00</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="P7" s="4" t="inlineStr">
         <is>
           <t>$75.3365</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="Q7" s="4" t="inlineStr">
         <is>
           <t>$4,404.17</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>TRT-0018</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>Marisela Thornbury</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>Sales</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>08/09/2021</t>
         </is>
       </c>
-      <c r="E8" t="n">
+      <c r="E8" s="4" t="n">
         <v>160</v>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F8" s="4" t="inlineStr">
         <is>
           <t>63.25</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>40.00</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>4.6154</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>4.6154</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>4.6154</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>4.6154</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>4.6154</t>
+        </is>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>4.6154</t>
+        </is>
+      </c>
+      <c r="K8" s="4" t="inlineStr">
         <is>
           <t>6.1538</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="L8" s="4" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="M8" s="4" t="inlineStr">
         <is>
           <t>60.00</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="N8" s="4" t="inlineStr">
         <is>
           <t>60.01</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="O8" s="4" t="inlineStr">
         <is>
           <t>$173,300.00</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="P8" s="4" t="inlineStr">
         <is>
           <t>$83.3173</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="Q8" s="4" t="inlineStr">
         <is>
           <t>$4,999.04</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>TRT-0021</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>Edith Bustamante</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>Customer Success</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>01/10/2022</t>
         </is>
       </c>
-      <c r="E9" t="n">
+      <c r="E9" s="4" t="n">
         <v>120</v>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>58.50</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G9" s="4" t="inlineStr">
         <is>
           <t>40.00</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>4.6154</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>4.6154</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>4.6154</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>4.6154</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>4.6154</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>4.6154</t>
+        </is>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>4.6154</t>
+        </is>
+      </c>
+      <c r="K9" s="4" t="inlineStr">
+        <is>
+          <t>4.6154</t>
+        </is>
+      </c>
+      <c r="L9" s="4" t="inlineStr">
         <is>
           <t>16.00</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="M9" s="4" t="inlineStr">
         <is>
           <t>42.46</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="N9" s="4" t="inlineStr">
         <is>
           <t>42.48</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="O9" s="4" t="inlineStr">
         <is>
           <t>$121,300.00</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="P9" s="4" t="inlineStr">
         <is>
           <t>$58.3173</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="Q9" s="4" t="inlineStr">
         <is>
           <t>$2,476.15</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>TRT-0023</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>Maeve Oyinlola</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>Engineering</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D10" s="4" t="inlineStr">
         <is>
           <t>02/14/2022</t>
         </is>
       </c>
-      <c r="E10" t="n">
+      <c r="E10" s="4" t="n">
         <v>120</v>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F10" s="4" t="inlineStr">
         <is>
           <t>60.50</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G10" s="4" t="inlineStr">
         <is>
           <t>40.00</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>4.6154</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>4.6154</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>4.6154</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>4.6154</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>4.6154</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>4.6154</t>
+        </is>
+      </c>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>4.6154</t>
+        </is>
+      </c>
+      <c r="K10" s="4" t="inlineStr">
+        <is>
+          <t>4.6154</t>
+        </is>
+      </c>
+      <c r="L10" s="4" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="M10" s="4" t="inlineStr">
         <is>
           <t>58.46</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="N10" s="4" t="inlineStr">
         <is>
           <t>58.48</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="O10" s="4" t="inlineStr">
         <is>
           <t>$154,900.00</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="P10" s="4" t="inlineStr">
         <is>
           <t>$74.4712</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="Q10" s="4" t="inlineStr">
         <is>
           <t>$4,353.59</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>TRT-0027</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>Kenji Abubakar</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>Marketing</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>01/24/2022</t>
         </is>
       </c>
-      <c r="E11" t="n">
+      <c r="E11" s="4" t="n">
         <v>120</v>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>24.25</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G11" s="4" t="inlineStr">
         <is>
           <t>24.25</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>4.6154</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>4.6154</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>4.6154</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>4.6154</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>4.6154</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>4.6154</t>
+        </is>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>4.6154</t>
+        </is>
+      </c>
+      <c r="K11" s="4" t="inlineStr">
+        <is>
+          <t>4.6154</t>
+        </is>
+      </c>
+      <c r="L11" s="4" t="inlineStr">
         <is>
           <t>16.00</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="M11" s="4" t="inlineStr">
         <is>
           <t>26.71</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="N11" s="4" t="inlineStr">
         <is>
           <t>26.73</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="O11" s="4" t="inlineStr">
         <is>
           <t>$157,600.00</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="P11" s="4" t="inlineStr">
         <is>
           <t>$75.7692</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="Q11" s="4" t="inlineStr">
         <is>
           <t>$2,023.80</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>TRT-0029</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>Emeka Thorsen</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>Sales</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D12" s="4" t="inlineStr">
         <is>
           <t>02/21/2022</t>
         </is>
       </c>
-      <c r="E12" t="n">
+      <c r="E12" s="4" t="n">
         <v>120</v>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F12" s="4" t="inlineStr">
         <is>
           <t>57.00</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G12" s="4" t="inlineStr">
         <is>
           <t>40.00</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>4.6154</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>4.6154</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>4.6154</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>4.6154</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>4.6154</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>4.6154</t>
+        </is>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>4.6154</t>
+        </is>
+      </c>
+      <c r="K12" s="4" t="inlineStr">
+        <is>
+          <t>4.6154</t>
+        </is>
+      </c>
+      <c r="L12" s="4" t="inlineStr">
         <is>
           <t>8.00</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="M12" s="4" t="inlineStr">
         <is>
           <t>50.46</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="N12" s="4" t="inlineStr">
         <is>
           <t>50.48</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="O12" s="4" t="inlineStr">
         <is>
           <t>$101,400.00</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="P12" s="4" t="inlineStr">
         <is>
           <t>$48.7500</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="Q12" s="4" t="inlineStr">
         <is>
           <t>$2,459.93</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>TRT-0031</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>Zephyr Adebayo</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>Engineering</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D13" s="4" t="inlineStr">
         <is>
           <t>03/07/2022</t>
         </is>
       </c>
-      <c r="E13" t="n">
+      <c r="E13" s="4" t="n">
         <v>120</v>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F13" s="4" t="inlineStr">
         <is>
           <t>52.00</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G13" s="4" t="inlineStr">
         <is>
           <t>40.00</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>4.6154</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>4.6154</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>4.6154</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>4.6154</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>4.6154</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>4.6154</t>
+        </is>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>4.6154</t>
+        </is>
+      </c>
+      <c r="K13" s="4" t="inlineStr">
+        <is>
+          <t>4.6154</t>
+        </is>
+      </c>
+      <c r="L13" s="4" t="inlineStr">
         <is>
           <t>32.00</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="M13" s="4" t="inlineStr">
         <is>
           <t>26.46</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="N13" s="4" t="inlineStr">
         <is>
           <t>26.48</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
+      <c r="O13" s="4" t="inlineStr">
         <is>
           <t>$161,200.00</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
+      <c r="P13" s="4" t="inlineStr">
         <is>
           <t>$77.5000</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr">
+      <c r="Q13" s="4" t="inlineStr">
         <is>
           <t>$2,050.65</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>TRT-0034</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>Luka Odum</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>Finance and Corporate</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D14" s="4" t="inlineStr">
         <is>
           <t>03/28/2022</t>
         </is>
       </c>
-      <c r="E14" t="n">
+      <c r="E14" s="4" t="n">
         <v>120</v>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F14" s="4" t="inlineStr">
         <is>
           <t>12.50</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="G14" s="4" t="inlineStr">
         <is>
           <t>12.50</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>4.6154</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>4.6154</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>4.6154</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>4.6154</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>4.6154</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>4.6154</t>
+        </is>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>4.6154</t>
+        </is>
+      </c>
+      <c r="K14" s="4" t="inlineStr">
+        <is>
+          <t>4.6154</t>
+        </is>
+      </c>
+      <c r="L14" s="4" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="M14" s="4" t="inlineStr">
         <is>
           <t>30.96</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="N14" s="4" t="inlineStr">
         <is>
           <t>30.98</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr">
+      <c r="O14" s="4" t="inlineStr">
         <is>
           <t>$84,600.00</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr">
+      <c r="P14" s="4" t="inlineStr">
         <is>
           <t>$40.6731</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr">
+      <c r="Q14" s="4" t="inlineStr">
         <is>
           <t>$1,259.24</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>TRT-0040</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>Ilse Van der Kolk</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>Product</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr">
         <is>
           <t>07/11/2022</t>
         </is>
       </c>
-      <c r="E15" t="n">
+      <c r="E15" s="4" t="n">
         <v>120</v>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F15" s="4" t="inlineStr">
         <is>
           <t>49.50</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="G15" s="4" t="inlineStr">
         <is>
           <t>40.00</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>4.6154</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>4.6154</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>4.6154</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>4.6154</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>4.6154</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>4.6154</t>
+        </is>
+      </c>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>4.6154</t>
+        </is>
+      </c>
+      <c r="K15" s="4" t="inlineStr">
+        <is>
+          <t>4.6154</t>
+        </is>
+      </c>
+      <c r="L15" s="4" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="M15" s="4" t="inlineStr">
         <is>
           <t>58.46</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
+      <c r="N15" s="4" t="inlineStr">
         <is>
           <t>58.48</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr">
+      <c r="O15" s="4" t="inlineStr">
         <is>
           <t>$176,400.00</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr">
+      <c r="P15" s="4" t="inlineStr">
         <is>
           <t>$84.8077</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr">
+      <c r="Q15" s="4" t="inlineStr">
         <is>
           <t>$4,957.86</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>TRT-0043</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>Oren Kastellanos</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>Sales</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D16" s="4" t="inlineStr">
         <is>
           <t>10/15/2021</t>
         </is>
       </c>
-      <c r="E16" t="n">
+      <c r="E16" s="4" t="n">
         <v>120</v>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F16" s="4" t="inlineStr">
         <is>
           <t>43.50</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="G16" s="4" t="inlineStr">
         <is>
           <t>40.00</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>4.6154</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>4.6154</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>4.6154</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>4.6154</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>4.6154</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>4.6154</t>
+        </is>
+      </c>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>4.6154</t>
+        </is>
+      </c>
+      <c r="K16" s="4" t="inlineStr">
+        <is>
+          <t>4.6154</t>
+        </is>
+      </c>
+      <c r="L16" s="4" t="inlineStr">
         <is>
           <t>24.00</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
+      <c r="M16" s="4" t="inlineStr">
         <is>
           <t>34.46</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
+      <c r="N16" s="4" t="inlineStr">
         <is>
           <t>34.48</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr">
+      <c r="O16" s="4" t="inlineStr">
         <is>
           <t>$97,350.00</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr">
+      <c r="P16" s="4" t="inlineStr">
         <is>
           <t>$46.8029</t>
         </is>
       </c>
-      <c r="Q16" t="inlineStr">
+      <c r="Q16" s="4" t="inlineStr">
         <is>
           <t>$1,612.83</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>TRT-0045</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>Thaddeus Ilunga</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t>Customer Success</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D17" s="4" t="inlineStr">
         <is>
           <t>07/25/2022</t>
         </is>
       </c>
-      <c r="E17" t="n">
+      <c r="E17" s="4" t="n">
         <v>120</v>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F17" s="4" t="inlineStr">
         <is>
           <t>29.50</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="G17" s="4" t="inlineStr">
         <is>
           <t>29.50</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>4.6154</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>4.6154</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>4.6154</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>4.6154</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>4.6154</t>
+        </is>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>4.6154</t>
+        </is>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>4.6154</t>
+        </is>
+      </c>
+      <c r="K17" s="4" t="inlineStr">
+        <is>
+          <t>4.6154</t>
+        </is>
+      </c>
+      <c r="L17" s="4" t="inlineStr">
         <is>
           <t>40.00</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr">
+      <c r="M17" s="4" t="inlineStr">
         <is>
           <t>7.96</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
+      <c r="N17" s="4" t="inlineStr">
         <is>
           <t>7.98</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr">
+      <c r="O17" s="4" t="inlineStr">
         <is>
           <t>$100,800.00</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr">
+      <c r="P17" s="4" t="inlineStr">
         <is>
           <t>$48.4615</t>
         </is>
       </c>
-      <c r="Q17" t="inlineStr">
+      <c r="Q17" s="4" t="inlineStr">
         <is>
           <t>$385.75</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="4" t="inlineStr">
         <is>
           <t>TRT-0047</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>Sunniva Mbeki</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C18" s="4" t="inlineStr">
         <is>
           <t>Engineering</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D18" s="4" t="inlineStr">
         <is>
           <t>12/05/2022</t>
         </is>
       </c>
-      <c r="E18" t="n">
+      <c r="E18" s="4" t="n">
         <v>120</v>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F18" s="4" t="inlineStr">
         <is>
           <t>19.00</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="G18" s="4" t="inlineStr">
         <is>
           <t>19.00</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>4.6154</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>4.6154</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>4.6154</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>4.6154</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>4.6154</t>
+        </is>
+      </c>
+      <c r="I18" s="4" t="inlineStr">
+        <is>
+          <t>4.6154</t>
+        </is>
+      </c>
+      <c r="J18" s="4" t="inlineStr">
+        <is>
+          <t>4.6154</t>
+        </is>
+      </c>
+      <c r="K18" s="4" t="inlineStr">
+        <is>
+          <t>4.6154</t>
+        </is>
+      </c>
+      <c r="L18" s="4" t="inlineStr">
         <is>
           <t>32.00</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr">
+      <c r="M18" s="4" t="inlineStr">
         <is>
           <t>5.46</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr">
+      <c r="N18" s="4" t="inlineStr">
         <is>
           <t>5.48</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr">
+      <c r="O18" s="4" t="inlineStr">
         <is>
           <t>$132,300.00</t>
         </is>
       </c>
-      <c r="P18" t="inlineStr">
+      <c r="P18" s="4" t="inlineStr">
         <is>
           <t>$63.6058</t>
         </is>
       </c>
-      <c r="Q18" t="inlineStr">
+      <c r="Q18" s="4" t="inlineStr">
         <is>
           <t>$347.29</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="4" t="inlineStr">
         <is>
           <t>TRT-0051</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>Priyamvada Raghunath</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C19" s="4" t="inlineStr">
         <is>
           <t>Engineering</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D19" s="4" t="inlineStr">
         <is>
           <t>05/03/2022</t>
         </is>
       </c>
-      <c r="E19" t="n">
+      <c r="E19" s="4" t="n">
         <v>120</v>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="F19" s="4" t="inlineStr">
         <is>
           <t>12.25</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="G19" s="4" t="inlineStr">
         <is>
           <t>12.25</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>4.6154</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>4.6154</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>4.6154</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>4.6154</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>4.6154</t>
+        </is>
+      </c>
+      <c r="I19" s="4" t="inlineStr">
+        <is>
+          <t>4.6154</t>
+        </is>
+      </c>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>4.6154</t>
+        </is>
+      </c>
+      <c r="K19" s="4" t="inlineStr">
+        <is>
+          <t>4.6154</t>
+        </is>
+      </c>
+      <c r="L19" s="4" t="inlineStr">
         <is>
           <t>24.00</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr">
+      <c r="M19" s="4" t="inlineStr">
         <is>
           <t>6.71</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr">
+      <c r="N19" s="4" t="inlineStr">
         <is>
           <t>6.73</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr">
+      <c r="O19" s="4" t="inlineStr">
         <is>
           <t>$129,800.00</t>
         </is>
       </c>
-      <c r="P19" t="inlineStr">
+      <c r="P19" s="4" t="inlineStr">
         <is>
           <t>$62.4038</t>
         </is>
       </c>
-      <c r="Q19" t="inlineStr">
+      <c r="Q19" s="4" t="inlineStr">
         <is>
           <t>$418.73</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="4" t="inlineStr">
         <is>
           <t>TRT-0052</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t>Persephone Adeyinka</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C20" s="4" t="inlineStr">
         <is>
           <t>Marketing</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D20" s="4" t="inlineStr">
         <is>
           <t>06/06/2022</t>
         </is>
       </c>
-      <c r="E20" t="n">
+      <c r="E20" s="4" t="n">
         <v>120</v>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F20" s="4" t="inlineStr">
         <is>
           <t>10.00</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="G20" s="4" t="inlineStr">
         <is>
           <t>10.00</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>4.6154</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>4.6154</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>4.6154</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>4.6154</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>4.6154</t>
+        </is>
+      </c>
+      <c r="I20" s="4" t="inlineStr">
+        <is>
+          <t>4.6154</t>
+        </is>
+      </c>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>4.6154</t>
+        </is>
+      </c>
+      <c r="K20" s="4" t="inlineStr">
+        <is>
+          <t>4.6154</t>
+        </is>
+      </c>
+      <c r="L20" s="4" t="inlineStr">
         <is>
           <t>24.00</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr">
+      <c r="M20" s="4" t="inlineStr">
         <is>
           <t>4.46</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr">
+      <c r="N20" s="4" t="inlineStr">
         <is>
           <t>4.48</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr">
+      <c r="O20" s="4" t="inlineStr">
         <is>
           <t>$103,700.00</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr">
+      <c r="P20" s="4" t="inlineStr">
         <is>
           <t>$49.8558</t>
         </is>
       </c>
-      <c r="Q20" t="inlineStr">
+      <c r="Q20" s="4" t="inlineStr">
         <is>
           <t>$222.36</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="4" t="inlineStr">
         <is>
           <t>TRT-0055</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>Ignatius Werahiko</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C21" s="4" t="inlineStr">
         <is>
           <t>Engineering</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D21" s="4" t="inlineStr">
         <is>
           <t>08/01/2022</t>
         </is>
       </c>
-      <c r="E21" t="n">
+      <c r="E21" s="4" t="n">
         <v>120</v>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F21" s="4" t="inlineStr">
         <is>
           <t>13.50</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="G21" s="4" t="inlineStr">
         <is>
           <t>13.50</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>4.6154</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>4.6154</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>4.6154</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>4.6154</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>4.6154</t>
+        </is>
+      </c>
+      <c r="I21" s="4" t="inlineStr">
+        <is>
+          <t>4.6154</t>
+        </is>
+      </c>
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t>4.6154</t>
+        </is>
+      </c>
+      <c r="K21" s="4" t="inlineStr">
+        <is>
+          <t>4.6154</t>
+        </is>
+      </c>
+      <c r="L21" s="4" t="inlineStr">
         <is>
           <t>16.00</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr">
+      <c r="M21" s="4" t="inlineStr">
         <is>
           <t>15.96</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr">
+      <c r="N21" s="4" t="inlineStr">
         <is>
           <t>15.98</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr">
+      <c r="O21" s="4" t="inlineStr">
         <is>
           <t>$130,450.00</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr">
+      <c r="P21" s="4" t="inlineStr">
         <is>
           <t>$62.7163</t>
         </is>
       </c>
-      <c r="Q21" t="inlineStr">
+      <c r="Q21" s="4" t="inlineStr">
         <is>
           <t>$1,000.95</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t>TRT-0058</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B22" s="4" t="inlineStr">
         <is>
           <t>Callum Oyelaran</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C22" s="4" t="inlineStr">
         <is>
           <t>Sales</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D22" s="4" t="inlineStr">
         <is>
           <t>09/12/2022</t>
         </is>
       </c>
-      <c r="E22" t="n">
+      <c r="E22" s="4" t="n">
         <v>120</v>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F22" s="4" t="inlineStr">
         <is>
           <t>22.50</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="G22" s="4" t="inlineStr">
         <is>
           <t>22.50</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>4.6154</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>4.6154</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>4.6154</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>4.6154</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>4.6154</t>
+        </is>
+      </c>
+      <c r="I22" s="4" t="inlineStr">
+        <is>
+          <t>4.6154</t>
+        </is>
+      </c>
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>4.6154</t>
+        </is>
+      </c>
+      <c r="K22" s="4" t="inlineStr">
+        <is>
+          <t>4.6154</t>
+        </is>
+      </c>
+      <c r="L22" s="4" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr">
+      <c r="M22" s="4" t="inlineStr">
         <is>
           <t>40.96</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr">
+      <c r="N22" s="4" t="inlineStr">
         <is>
           <t>40.98</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr">
+      <c r="O22" s="4" t="inlineStr">
         <is>
           <t>$94,750.00</t>
         </is>
       </c>
-      <c r="P22" t="inlineStr">
+      <c r="P22" s="4" t="inlineStr">
         <is>
           <t>$45.5529</t>
         </is>
       </c>
-      <c r="Q22" t="inlineStr">
+      <c r="Q22" s="4" t="inlineStr">
         <is>
           <t>$1,865.85</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="A23" s="4" t="inlineStr">
         <is>
           <t>TRT-0062</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B23" s="4" t="inlineStr">
         <is>
           <t>Tina Jung</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C23" s="4" t="inlineStr">
         <is>
           <t>Engineering</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D23" s="4" t="inlineStr">
         <is>
           <t>11/14/2022</t>
         </is>
       </c>
-      <c r="E23" t="n">
+      <c r="E23" s="4" t="n">
         <v>120</v>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="F23" s="4" t="inlineStr">
         <is>
           <t>10.75</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="G23" s="4" t="inlineStr">
         <is>
           <t>10.75</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>4.6154</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>4.6154</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>4.6154</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>4.6154</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>4.6154</t>
+        </is>
+      </c>
+      <c r="I23" s="4" t="inlineStr">
+        <is>
+          <t>4.6154</t>
+        </is>
+      </c>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>4.6154</t>
+        </is>
+      </c>
+      <c r="K23" s="4" t="inlineStr">
+        <is>
+          <t>4.6154</t>
+        </is>
+      </c>
+      <c r="L23" s="4" t="inlineStr">
         <is>
           <t>8.00</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr">
+      <c r="M23" s="4" t="inlineStr">
         <is>
           <t>21.21</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr">
+      <c r="N23" s="4" t="inlineStr">
         <is>
           <t>21.23</t>
         </is>
       </c>
-      <c r="O23" t="inlineStr">
+      <c r="O23" s="4" t="inlineStr">
         <is>
           <t>$152,600.00</t>
         </is>
       </c>
-      <c r="P23" t="inlineStr">
+      <c r="P23" s="4" t="inlineStr">
         <is>
           <t>$73.3654</t>
         </is>
       </c>
-      <c r="Q23" t="inlineStr">
+      <c r="Q23" s="4" t="inlineStr">
         <is>
           <t>$1,556.08</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="A24" s="4" t="inlineStr">
         <is>
           <t>TRT-0066</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B24" s="4" t="inlineStr">
         <is>
           <t>Tomasz Ekwueme</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C24" s="4" t="inlineStr">
         <is>
           <t>Engineering</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D24" s="4" t="inlineStr">
         <is>
           <t>01/09/2023</t>
         </is>
       </c>
-      <c r="E24" t="n">
+      <c r="E24" s="4" t="n">
         <v>120</v>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F24" s="4" t="inlineStr">
         <is>
           <t>9.50</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="G24" s="4" t="inlineStr">
         <is>
           <t>9.50</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>4.6154</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>4.6154</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>4.6154</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>4.6154</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t>4.6154</t>
+        </is>
+      </c>
+      <c r="I24" s="4" t="inlineStr">
+        <is>
+          <t>4.6154</t>
+        </is>
+      </c>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>4.6154</t>
+        </is>
+      </c>
+      <c r="K24" s="4" t="inlineStr">
+        <is>
+          <t>4.6154</t>
+        </is>
+      </c>
+      <c r="L24" s="4" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr">
+      <c r="M24" s="4" t="inlineStr">
         <is>
           <t>27.96</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr">
+      <c r="N24" s="4" t="inlineStr">
         <is>
           <t>27.98</t>
         </is>
       </c>
-      <c r="O24" t="inlineStr">
+      <c r="O24" s="4" t="inlineStr">
         <is>
           <t>$179,800.00</t>
         </is>
       </c>
-      <c r="P24" t="inlineStr">
+      <c r="P24" s="4" t="inlineStr">
         <is>
           <t>$86.4423</t>
         </is>
       </c>
-      <c r="Q24" t="inlineStr">
+      <c r="Q24" s="4" t="inlineStr">
         <is>
           <t>$2,416.93</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A25" s="4" t="inlineStr">
         <is>
           <t>TRT-0069</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B25" s="4" t="inlineStr">
         <is>
           <t>Xiomara Bekele</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C25" s="4" t="inlineStr">
         <is>
           <t>Customer Success</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D25" s="4" t="inlineStr">
         <is>
           <t>05/15/2023</t>
         </is>
       </c>
-      <c r="E25" t="n">
+      <c r="E25" s="4" t="n">
         <v>120</v>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F25" s="4" t="inlineStr">
         <is>
           <t>27.75</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="G25" s="4" t="inlineStr">
         <is>
           <t>27.75</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>4.6154</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>4.6154</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>4.6154</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>4.6154</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>4.6154</t>
+        </is>
+      </c>
+      <c r="I25" s="4" t="inlineStr">
+        <is>
+          <t>4.6154</t>
+        </is>
+      </c>
+      <c r="J25" s="4" t="inlineStr">
+        <is>
+          <t>4.6154</t>
+        </is>
+      </c>
+      <c r="K25" s="4" t="inlineStr">
+        <is>
+          <t>4.6154</t>
+        </is>
+      </c>
+      <c r="L25" s="4" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr">
+      <c r="M25" s="4" t="inlineStr">
         <is>
           <t>46.21</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr">
+      <c r="N25" s="4" t="inlineStr">
         <is>
           <t>46.23</t>
         </is>
       </c>
-      <c r="O25" t="inlineStr">
+      <c r="O25" s="4" t="inlineStr">
         <is>
           <t>$99,300.00</t>
         </is>
       </c>
-      <c r="P25" t="inlineStr">
+      <c r="P25" s="4" t="inlineStr">
         <is>
           <t>$47.7404</t>
         </is>
       </c>
-      <c r="Q25" t="inlineStr">
+      <c r="Q25" s="4" t="inlineStr">
         <is>
           <t>$2,206.08</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="A26" s="4" t="inlineStr">
         <is>
           <t>TRT-0071</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B26" s="4" t="inlineStr">
         <is>
           <t>Samuel Burkenham</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C26" s="4" t="inlineStr">
         <is>
           <t>Product</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D26" s="4" t="inlineStr">
         <is>
           <t>03/08/2021</t>
         </is>
       </c>
-      <c r="E26" t="n">
+      <c r="E26" s="4" t="n">
         <v>160</v>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="F26" s="4" t="inlineStr">
         <is>
           <t>27.25</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="G26" s="4" t="inlineStr">
         <is>
           <t>27.25</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="H26" s="4" t="inlineStr">
         <is>
           <t>6.1538</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="I26" s="4" t="inlineStr">
         <is>
           <t>6.1538</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
+      <c r="J26" s="4" t="inlineStr">
         <is>
           <t>6.1538</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
+      <c r="K26" s="4" t="inlineStr">
         <is>
           <t>6.1538</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="L26" s="4" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr">
+      <c r="M26" s="4" t="inlineStr">
         <is>
           <t>51.87</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr">
+      <c r="N26" s="4" t="inlineStr">
         <is>
           <t>51.85</t>
         </is>
       </c>
-      <c r="O26" t="inlineStr">
+      <c r="O26" s="4" t="inlineStr">
         <is>
           <t>$81,000.00</t>
         </is>
       </c>
-      <c r="P26" t="inlineStr">
+      <c r="P26" s="4" t="inlineStr">
         <is>
           <t>$38.9423</t>
         </is>
       </c>
-      <c r="Q26" t="inlineStr">
+      <c r="Q26" s="4" t="inlineStr">
         <is>
           <t>$2,019.94</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
+      <c r="A27" s="4" t="inlineStr">
         <is>
           <t>TRT-0074</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B27" s="4" t="inlineStr">
         <is>
           <t>Cassius Oyelowo</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C27" s="4" t="inlineStr">
         <is>
           <t>Engineering</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D27" s="4" t="inlineStr">
         <is>
           <t>09/18/2023</t>
         </is>
       </c>
-      <c r="E27" t="n">
+      <c r="E27" s="4" t="n">
         <v>120</v>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="F27" s="4" t="inlineStr">
         <is>
           <t>25.75</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="G27" s="4" t="inlineStr">
         <is>
           <t>25.75</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>4.6154</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>4.6154</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>4.6154</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>4.6154</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
+      <c r="H27" s="4" t="inlineStr">
+        <is>
+          <t>4.6154</t>
+        </is>
+      </c>
+      <c r="I27" s="4" t="inlineStr">
+        <is>
+          <t>4.6154</t>
+        </is>
+      </c>
+      <c r="J27" s="4" t="inlineStr">
+        <is>
+          <t>4.6154</t>
+        </is>
+      </c>
+      <c r="K27" s="4" t="inlineStr">
+        <is>
+          <t>4.6154</t>
+        </is>
+      </c>
+      <c r="L27" s="4" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr">
+      <c r="M27" s="4" t="inlineStr">
         <is>
           <t>44.21</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr">
+      <c r="N27" s="4" t="inlineStr">
         <is>
           <t>44.23</t>
         </is>
       </c>
-      <c r="O27" t="inlineStr">
+      <c r="O27" s="4" t="inlineStr">
         <is>
           <t>$111,800.00</t>
         </is>
       </c>
-      <c r="P27" t="inlineStr">
+      <c r="P27" s="4" t="inlineStr">
         <is>
           <t>$53.7500</t>
         </is>
       </c>
-      <c r="Q27" t="inlineStr">
+      <c r="Q27" s="4" t="inlineStr">
         <is>
           <t>$2,376.29</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="A28" s="4" t="inlineStr">
         <is>
           <t>TRT-0076</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B28" s="4" t="inlineStr">
         <is>
           <t>Nikolai Oyeleke</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C28" s="4" t="inlineStr">
         <is>
           <t>Product</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D28" s="4" t="inlineStr">
         <is>
           <t>10/02/2023</t>
         </is>
       </c>
-      <c r="E28" t="n">
+      <c r="E28" s="4" t="n">
         <v>120</v>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="F28" s="4" t="inlineStr">
         <is>
           <t>24.75</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="G28" s="4" t="inlineStr">
         <is>
           <t>24.75</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>4.6154</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>4.6154</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>4.6154</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>4.6154</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t>4.6154</t>
+        </is>
+      </c>
+      <c r="I28" s="4" t="inlineStr">
+        <is>
+          <t>4.6154</t>
+        </is>
+      </c>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>4.6154</t>
+        </is>
+      </c>
+      <c r="K28" s="4" t="inlineStr">
+        <is>
+          <t>4.6154</t>
+        </is>
+      </c>
+      <c r="L28" s="4" t="inlineStr">
         <is>
           <t>8.00</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr">
+      <c r="M28" s="4" t="inlineStr">
         <is>
           <t>35.21</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr">
+      <c r="N28" s="4" t="inlineStr">
         <is>
           <t>35.23</t>
         </is>
       </c>
-      <c r="O28" t="inlineStr">
+      <c r="O28" s="4" t="inlineStr">
         <is>
           <t>$151,900.00</t>
         </is>
       </c>
-      <c r="P28" t="inlineStr">
+      <c r="P28" s="4" t="inlineStr">
         <is>
           <t>$73.0288</t>
         </is>
       </c>
-      <c r="Q28" t="inlineStr">
+      <c r="Q28" s="4" t="inlineStr">
         <is>
           <t>$2,571.34</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
+      <c r="A29" s="4" t="inlineStr">
         <is>
           <t>TRT-0079</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B29" s="4" t="inlineStr">
         <is>
           <t>Wren Takahashi-Bell</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C29" s="4" t="inlineStr">
         <is>
           <t>Product</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D29" s="4" t="inlineStr">
         <is>
           <t>02/06/2023</t>
         </is>
       </c>
-      <c r="E29" t="n">
+      <c r="E29" s="4" t="n">
         <v>120</v>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="F29" s="4" t="inlineStr">
         <is>
           <t>6.50</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="G29" s="4" t="inlineStr">
         <is>
           <t>6.50</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>4.6154</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>4.6154</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>4.6154</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>4.6154</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
+      <c r="H29" s="4" t="inlineStr">
+        <is>
+          <t>4.6154</t>
+        </is>
+      </c>
+      <c r="I29" s="4" t="inlineStr">
+        <is>
+          <t>4.6154</t>
+        </is>
+      </c>
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>4.6154</t>
+        </is>
+      </c>
+      <c r="K29" s="4" t="inlineStr">
+        <is>
+          <t>4.6154</t>
+        </is>
+      </c>
+      <c r="L29" s="4" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr">
+      <c r="M29" s="4" t="inlineStr">
         <is>
           <t>24.96</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr">
+      <c r="N29" s="4" t="inlineStr">
         <is>
           <t>24.98</t>
         </is>
       </c>
-      <c r="O29" t="inlineStr">
+      <c r="O29" s="4" t="inlineStr">
         <is>
           <t>$119,600.00</t>
         </is>
       </c>
-      <c r="P29" t="inlineStr">
+      <c r="P29" s="4" t="inlineStr">
         <is>
           <t>$57.5000</t>
         </is>
       </c>
-      <c r="Q29" t="inlineStr">
+      <c r="Q29" s="4" t="inlineStr">
         <is>
           <t>$1,435.20</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
+      <c r="A30" s="4" t="inlineStr">
         <is>
           <t>TRT-0083</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B30" s="4" t="inlineStr">
         <is>
           <t>Desmond Achterberg</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C30" s="4" t="inlineStr">
         <is>
           <t>Customer Success</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D30" s="4" t="inlineStr">
         <is>
           <t>06/19/2023</t>
         </is>
       </c>
-      <c r="E30" t="n">
+      <c r="E30" s="4" t="n">
         <v>120</v>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="F30" s="4" t="inlineStr">
         <is>
           <t>32.25</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="G30" s="4" t="inlineStr">
         <is>
           <t>32.25</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>4.6154</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>4.6154</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>4.6154</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>4.6154</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr">
+      <c r="H30" s="4" t="inlineStr">
+        <is>
+          <t>4.6154</t>
+        </is>
+      </c>
+      <c r="I30" s="4" t="inlineStr">
+        <is>
+          <t>4.6154</t>
+        </is>
+      </c>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>4.6154</t>
+        </is>
+      </c>
+      <c r="K30" s="4" t="inlineStr">
+        <is>
+          <t>4.6154</t>
+        </is>
+      </c>
+      <c r="L30" s="4" t="inlineStr">
         <is>
           <t>32.00</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr">
+      <c r="M30" s="4" t="inlineStr">
         <is>
           <t>18.71</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr">
+      <c r="N30" s="4" t="inlineStr">
         <is>
           <t>18.73</t>
         </is>
       </c>
-      <c r="O30" t="inlineStr">
+      <c r="O30" s="4" t="inlineStr">
         <is>
           <t>$93,100.00</t>
         </is>
       </c>
-      <c r="P30" t="inlineStr">
+      <c r="P30" s="4" t="inlineStr">
         <is>
           <t>$44.7596</t>
         </is>
       </c>
-      <c r="Q30" t="inlineStr">
+      <c r="Q30" s="4" t="inlineStr">
         <is>
           <t>$837.45</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="A31" s="4" t="inlineStr">
         <is>
           <t>TRT-0086</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B31" s="4" t="inlineStr">
         <is>
           <t>Rosalind Munro</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C31" s="4" t="inlineStr">
         <is>
           <t>Sales</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D31" s="4" t="inlineStr">
         <is>
           <t>08/28/2023</t>
         </is>
       </c>
-      <c r="E31" t="n">
+      <c r="E31" s="4" t="n">
         <v>120</v>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="F31" s="4" t="inlineStr">
         <is>
           <t>33.50</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="G31" s="4" t="inlineStr">
         <is>
           <t>33.50</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>4.6154</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>4.6154</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>4.6154</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>4.6154</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
+      <c r="H31" s="4" t="inlineStr">
+        <is>
+          <t>4.6154</t>
+        </is>
+      </c>
+      <c r="I31" s="4" t="inlineStr">
+        <is>
+          <t>4.6154</t>
+        </is>
+      </c>
+      <c r="J31" s="4" t="inlineStr">
+        <is>
+          <t>4.6154</t>
+        </is>
+      </c>
+      <c r="K31" s="4" t="inlineStr">
+        <is>
+          <t>4.6154</t>
+        </is>
+      </c>
+      <c r="L31" s="4" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="M31" t="inlineStr">
+      <c r="M31" s="4" t="inlineStr">
         <is>
           <t>51.96</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr">
+      <c r="N31" s="4" t="inlineStr">
         <is>
           <t>51.98</t>
         </is>
       </c>
-      <c r="O31" t="inlineStr">
+      <c r="O31" s="4" t="inlineStr">
         <is>
           <t>$63,750.00</t>
         </is>
       </c>
-      <c r="P31" t="inlineStr">
+      <c r="P31" s="4" t="inlineStr">
         <is>
           <t>$30.6490</t>
         </is>
       </c>
-      <c r="Q31" t="inlineStr">
+      <c r="Q31" s="4" t="inlineStr">
         <is>
           <t>$1,592.52</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
+      <c r="A32" s="4" t="inlineStr">
         <is>
           <t>TRT-0088</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B32" s="4" t="inlineStr">
         <is>
           <t>Yolanda Featherstone</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C32" s="4" t="inlineStr">
         <is>
           <t>Customer Success</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="D32" s="4" t="inlineStr">
         <is>
           <t>07/17/2023</t>
         </is>
       </c>
-      <c r="E32" t="n">
+      <c r="E32" s="4" t="n">
         <v>120</v>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="F32" s="4" t="inlineStr">
         <is>
           <t>34.75</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="G32" s="4" t="inlineStr">
         <is>
           <t>34.75</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>4.6154</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>4.6154</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>4.6154</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>4.6154</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr">
+      <c r="H32" s="4" t="inlineStr">
+        <is>
+          <t>4.6154</t>
+        </is>
+      </c>
+      <c r="I32" s="4" t="inlineStr">
+        <is>
+          <t>4.6154</t>
+        </is>
+      </c>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>4.6154</t>
+        </is>
+      </c>
+      <c r="K32" s="4" t="inlineStr">
+        <is>
+          <t>4.6154</t>
+        </is>
+      </c>
+      <c r="L32" s="4" t="inlineStr">
         <is>
           <t>40.00</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr">
+      <c r="M32" s="4" t="inlineStr">
         <is>
           <t>13.21</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr">
+      <c r="N32" s="4" t="inlineStr">
         <is>
           <t>13.23</t>
         </is>
       </c>
-      <c r="O32" t="inlineStr">
+      <c r="O32" s="4" t="inlineStr">
         <is>
           <t>$118,000.00</t>
         </is>
       </c>
-      <c r="P32" t="inlineStr">
+      <c r="P32" s="4" t="inlineStr">
         <is>
           <t>$56.7308</t>
         </is>
       </c>
-      <c r="Q32" t="inlineStr">
+      <c r="Q32" s="4" t="inlineStr">
         <is>
           <t>$749.41</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
+      <c r="A33" s="4" t="inlineStr">
         <is>
           <t>TRT-0091</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B33" s="4" t="inlineStr">
         <is>
           <t>Beatrix Nakagawa</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C33" s="4" t="inlineStr">
         <is>
           <t>Engineering</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="D33" s="4" t="inlineStr">
         <is>
           <t>11/06/2023</t>
         </is>
       </c>
-      <c r="E33" t="n">
+      <c r="E33" s="4" t="n">
         <v>120</v>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="F33" s="4" t="inlineStr">
         <is>
           <t>7.25</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="G33" s="4" t="inlineStr">
         <is>
           <t>7.25</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>4.6154</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>4.6154</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>4.6154</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>4.6154</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
+      <c r="H33" s="4" t="inlineStr">
+        <is>
+          <t>4.6154</t>
+        </is>
+      </c>
+      <c r="I33" s="4" t="inlineStr">
+        <is>
+          <t>4.6154</t>
+        </is>
+      </c>
+      <c r="J33" s="4" t="inlineStr">
+        <is>
+          <t>4.6154</t>
+        </is>
+      </c>
+      <c r="K33" s="4" t="inlineStr">
+        <is>
+          <t>4.6154</t>
+        </is>
+      </c>
+      <c r="L33" s="4" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr">
+      <c r="M33" s="4" t="inlineStr">
         <is>
           <t>25.71</t>
         </is>
       </c>
-      <c r="N33" t="inlineStr">
+      <c r="N33" s="4" t="inlineStr">
         <is>
           <t>25.73</t>
         </is>
       </c>
-      <c r="O33" t="inlineStr">
+      <c r="O33" s="4" t="inlineStr">
         <is>
           <t>$144,500.00</t>
         </is>
       </c>
-      <c r="P33" t="inlineStr">
+      <c r="P33" s="4" t="inlineStr">
         <is>
           <t>$69.4712</t>
         </is>
       </c>
-      <c r="Q33" t="inlineStr">
+      <c r="Q33" s="4" t="inlineStr">
         <is>
           <t>$1,786.10</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
+      <c r="A34" s="4" t="inlineStr">
         <is>
           <t>TRT-0093</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B34" s="4" t="inlineStr">
         <is>
           <t>Caspian Nwachukwu</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C34" s="4" t="inlineStr">
         <is>
           <t>Marketing</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="D34" s="4" t="inlineStr">
         <is>
           <t>12/11/2023</t>
         </is>
       </c>
-      <c r="E34" t="n">
+      <c r="E34" s="4" t="n">
         <v>120</v>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="F34" s="4" t="inlineStr">
         <is>
           <t>33.75</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="G34" s="4" t="inlineStr">
         <is>
           <t>33.75</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>4.6154</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>4.6154</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>4.6154</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>4.6154</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr">
+      <c r="H34" s="4" t="inlineStr">
+        <is>
+          <t>4.6154</t>
+        </is>
+      </c>
+      <c r="I34" s="4" t="inlineStr">
+        <is>
+          <t>4.6154</t>
+        </is>
+      </c>
+      <c r="J34" s="4" t="inlineStr">
+        <is>
+          <t>4.6154</t>
+        </is>
+      </c>
+      <c r="K34" s="4" t="inlineStr">
+        <is>
+          <t>4.6154</t>
+        </is>
+      </c>
+      <c r="L34" s="4" t="inlineStr">
         <is>
           <t>32.00</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr">
+      <c r="M34" s="4" t="inlineStr">
         <is>
           <t>20.21</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr">
+      <c r="N34" s="4" t="inlineStr">
         <is>
           <t>20.23</t>
         </is>
       </c>
-      <c r="O34" t="inlineStr">
+      <c r="O34" s="4" t="inlineStr">
         <is>
           <t>$109,300.00</t>
         </is>
       </c>
-      <c r="P34" t="inlineStr">
+      <c r="P34" s="4" t="inlineStr">
         <is>
           <t>$52.5481</t>
         </is>
       </c>
-      <c r="Q34" t="inlineStr">
+      <c r="Q34" s="4" t="inlineStr">
         <is>
           <t>$1,062.00</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
+      <c r="A35" s="4" t="inlineStr">
         <is>
           <t>TRT-0096</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B35" s="4" t="inlineStr">
         <is>
           <t>Delphine Marchetti</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C35" s="4" t="inlineStr">
         <is>
           <t>Customer Success</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="D35" s="4" t="inlineStr">
         <is>
           <t>08/17/2025</t>
         </is>
       </c>
-      <c r="E35" t="n">
+      <c r="E35" s="4" t="n">
         <v>80</v>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="F35" s="4" t="inlineStr">
         <is>
           <t>24.25</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="G35" s="4" t="inlineStr">
         <is>
           <t>24.25</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
+      <c r="H35" s="4" t="inlineStr">
         <is>
           <t>3.0769</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
+      <c r="I35" s="4" t="inlineStr">
         <is>
           <t>3.0769</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr">
+      <c r="J35" s="4" t="inlineStr">
         <is>
           <t>3.0769</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr">
+      <c r="K35" s="4" t="inlineStr">
         <is>
           <t>3.0769</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr">
+      <c r="L35" s="4" t="inlineStr">
         <is>
           <t>16.00</t>
         </is>
       </c>
-      <c r="M35" t="inlineStr">
+      <c r="M35" s="4" t="inlineStr">
         <is>
           <t>20.56</t>
         </is>
       </c>
-      <c r="N35" t="inlineStr">
+      <c r="N35" s="4" t="inlineStr">
         <is>
           <t>20.57</t>
         </is>
       </c>
-      <c r="O35" t="inlineStr">
+      <c r="O35" s="4" t="inlineStr">
         <is>
           <t>$61,000.00</t>
         </is>
       </c>
-      <c r="P35" t="inlineStr">
+      <c r="P35" s="4" t="inlineStr">
         <is>
           <t>$29.3269</t>
         </is>
       </c>
-      <c r="Q35" t="inlineStr">
+      <c r="Q35" s="4" t="inlineStr">
         <is>
           <t>$602.96</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
+      <c r="A36" s="4" t="inlineStr">
         <is>
           <t>TRT-0099</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B36" s="4" t="inlineStr">
         <is>
           <t>Leopold Anyanwu</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C36" s="4" t="inlineStr">
         <is>
           <t>Customer Success</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="D36" s="4" t="inlineStr">
         <is>
           <t>12/09/2024</t>
         </is>
       </c>
-      <c r="E36" t="n">
+      <c r="E36" s="4" t="n">
         <v>80</v>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="F36" s="4" t="inlineStr">
         <is>
           <t>24.75</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="G36" s="4" t="inlineStr">
         <is>
           <t>24.75</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
+      <c r="H36" s="4" t="inlineStr">
         <is>
           <t>3.0769</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
+      <c r="I36" s="4" t="inlineStr">
         <is>
           <t>3.0769</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr">
+      <c r="J36" s="4" t="inlineStr">
         <is>
           <t>3.0769</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr">
+      <c r="K36" s="4" t="inlineStr">
         <is>
           <t>3.0769</t>
         </is>
       </c>
-      <c r="L36" t="inlineStr">
+      <c r="L36" s="4" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="M36" t="inlineStr">
+      <c r="M36" s="4" t="inlineStr">
         <is>
           <t>37.06</t>
         </is>
       </c>
-      <c r="N36" t="inlineStr">
+      <c r="N36" s="4" t="inlineStr">
         <is>
           <t>37.07</t>
         </is>
       </c>
-      <c r="O36" t="inlineStr">
+      <c r="O36" s="4" t="inlineStr">
         <is>
           <t>$77,650.00</t>
         </is>
       </c>
-      <c r="P36" t="inlineStr">
+      <c r="P36" s="4" t="inlineStr">
         <is>
           <t>$37.3317</t>
         </is>
       </c>
-      <c r="Q36" t="inlineStr">
+      <c r="Q36" s="4" t="inlineStr">
         <is>
           <t>$1,383.51</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
+      <c r="A37" s="4" t="inlineStr">
         <is>
           <t>TRT-0102</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B37" s="4" t="inlineStr">
         <is>
           <t>Lucía Ferrante</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C37" s="4" t="inlineStr">
         <is>
           <t>Engineering</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="D37" s="4" t="inlineStr">
         <is>
           <t>01/20/2025</t>
         </is>
       </c>
-      <c r="E37" t="n">
+      <c r="E37" s="4" t="n">
         <v>80</v>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="F37" s="4" t="inlineStr">
         <is>
           <t>12.00</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="G37" s="4" t="inlineStr">
         <is>
           <t>12.00</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
+      <c r="H37" s="4" t="inlineStr">
         <is>
           <t>3.0769</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
+      <c r="I37" s="4" t="inlineStr">
         <is>
           <t>3.0769</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr">
+      <c r="J37" s="4" t="inlineStr">
         <is>
           <t>3.0769</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr">
+      <c r="K37" s="4" t="inlineStr">
         <is>
           <t>3.0769</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr">
+      <c r="L37" s="4" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="M37" t="inlineStr">
+      <c r="M37" s="4" t="inlineStr">
         <is>
           <t>24.31</t>
         </is>
       </c>
-      <c r="N37" t="inlineStr">
+      <c r="N37" s="4" t="inlineStr">
         <is>
           <t>24.32</t>
         </is>
       </c>
-      <c r="O37" t="inlineStr">
+      <c r="O37" s="4" t="inlineStr">
         <is>
           <t>$108,900.00</t>
         </is>
       </c>
-      <c r="P37" t="inlineStr">
+      <c r="P37" s="4" t="inlineStr">
         <is>
           <t>$52.3558</t>
         </is>
       </c>
-      <c r="Q37" t="inlineStr">
+      <c r="Q37" s="4" t="inlineStr">
         <is>
           <t>$1,272.77</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
+      <c r="A38" s="4" t="inlineStr">
         <is>
           <t>TRT-0105</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B38" s="4" t="inlineStr">
         <is>
           <t>Olamide Fitzwilliam</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C38" s="4" t="inlineStr">
         <is>
           <t>Engineering</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="D38" s="4" t="inlineStr">
         <is>
           <t>02/24/2025</t>
         </is>
       </c>
-      <c r="E38" t="n">
+      <c r="E38" s="4" t="n">
         <v>80</v>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="F38" s="4" t="inlineStr">
         <is>
           <t>27.50</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="G38" s="4" t="inlineStr">
         <is>
           <t>27.50</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
+      <c r="H38" s="4" t="inlineStr">
         <is>
           <t>3.0769</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
+      <c r="I38" s="4" t="inlineStr">
         <is>
           <t>3.0769</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr">
+      <c r="J38" s="4" t="inlineStr">
         <is>
           <t>3.0769</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr">
+      <c r="K38" s="4" t="inlineStr">
         <is>
           <t>3.0769</t>
         </is>
       </c>
-      <c r="L38" t="inlineStr">
+      <c r="L38" s="4" t="inlineStr">
         <is>
           <t>24.00</t>
         </is>
       </c>
-      <c r="M38" t="inlineStr">
+      <c r="M38" s="4" t="inlineStr">
         <is>
           <t>15.81</t>
         </is>
       </c>
-      <c r="N38" t="inlineStr">
+      <c r="N38" s="4" t="inlineStr">
         <is>
           <t>15.82</t>
         </is>
       </c>
-      <c r="O38" t="inlineStr">
+      <c r="O38" s="4" t="inlineStr">
         <is>
           <t>$109,200.00</t>
         </is>
       </c>
-      <c r="P38" t="inlineStr">
+      <c r="P38" s="4" t="inlineStr">
         <is>
           <t>$52.5000</t>
         </is>
       </c>
-      <c r="Q38" t="inlineStr">
+      <c r="Q38" s="4" t="inlineStr">
         <is>
           <t>$830.02</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
+      <c r="A39" s="4" t="inlineStr">
         <is>
           <t>TRT-0108</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B39" s="4" t="inlineStr">
         <is>
           <t>Gideon Marlowe</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="C39" s="4" t="inlineStr">
         <is>
           <t>Sales</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="D39" s="4" t="inlineStr">
         <is>
           <t>03/03/2025</t>
         </is>
       </c>
-      <c r="E39" t="n">
+      <c r="E39" s="4" t="n">
         <v>80</v>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="F39" s="4" t="inlineStr">
         <is>
           <t>37.00</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="G39" s="4" t="inlineStr">
         <is>
           <t>37.00</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
+      <c r="H39" s="4" t="inlineStr">
         <is>
           <t>3.0769</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
+      <c r="I39" s="4" t="inlineStr">
         <is>
           <t>3.0769</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr">
+      <c r="J39" s="4" t="inlineStr">
         <is>
           <t>3.0769</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr">
+      <c r="K39" s="4" t="inlineStr">
         <is>
           <t>3.0769</t>
         </is>
       </c>
-      <c r="L39" t="inlineStr">
+      <c r="L39" s="4" t="inlineStr">
         <is>
           <t>8.00</t>
         </is>
       </c>
-      <c r="M39" t="inlineStr">
+      <c r="M39" s="4" t="inlineStr">
         <is>
           <t>41.31</t>
         </is>
       </c>
-      <c r="N39" t="inlineStr">
+      <c r="N39" s="4" t="inlineStr">
         <is>
           <t>41.32</t>
         </is>
       </c>
-      <c r="O39" t="inlineStr">
+      <c r="O39" s="4" t="inlineStr">
         <is>
           <t>$95,850.00</t>
         </is>
       </c>
-      <c r="P39" t="inlineStr">
+      <c r="P39" s="4" t="inlineStr">
         <is>
           <t>$46.0817</t>
         </is>
       </c>
-      <c r="Q39" t="inlineStr">
+      <c r="Q39" s="4" t="inlineStr">
         <is>
           <t>$1,903.64</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
+      <c r="A40" s="4" t="inlineStr">
         <is>
           <t>TRT-0110</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B40" s="4" t="inlineStr">
         <is>
           <t>Bartholomew Oduya</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C40" s="4" t="inlineStr">
         <is>
           <t>Sales</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="D40" s="4" t="inlineStr">
         <is>
           <t>03/17/2025</t>
         </is>
       </c>
-      <c r="E40" t="n">
+      <c r="E40" s="4" t="n">
         <v>80</v>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="F40" s="4" t="inlineStr">
         <is>
           <t>11.50</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="G40" s="4" t="inlineStr">
         <is>
           <t>11.50</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
+      <c r="H40" s="4" t="inlineStr">
         <is>
           <t>3.0769</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
+      <c r="I40" s="4" t="inlineStr">
         <is>
           <t>3.0769</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr">
+      <c r="J40" s="4" t="inlineStr">
         <is>
           <t>3.0769</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr">
+      <c r="K40" s="4" t="inlineStr">
         <is>
           <t>3.0769</t>
         </is>
       </c>
-      <c r="L40" t="inlineStr">
+      <c r="L40" s="4" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="M40" t="inlineStr">
+      <c r="M40" s="4" t="inlineStr">
         <is>
           <t>23.81</t>
         </is>
       </c>
-      <c r="N40" t="inlineStr">
+      <c r="N40" s="4" t="inlineStr">
         <is>
           <t>23.82</t>
         </is>
       </c>
-      <c r="O40" t="inlineStr">
+      <c r="O40" s="4" t="inlineStr">
         <is>
           <t>$91,200.00</t>
         </is>
       </c>
-      <c r="P40" t="inlineStr">
+      <c r="P40" s="4" t="inlineStr">
         <is>
           <t>$43.8462</t>
         </is>
       </c>
-      <c r="Q40" t="inlineStr">
+      <c r="Q40" s="4" t="inlineStr">
         <is>
           <t>$1,043.98</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
+      <c r="A41" s="4" t="inlineStr">
         <is>
           <t>TRT-0113</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B41" s="4" t="inlineStr">
         <is>
           <t>Winnie Barslanian</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C41" s="4" t="inlineStr">
         <is>
           <t>Customer Success</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="D41" s="4" t="inlineStr">
         <is>
           <t>04/07/2025</t>
         </is>
       </c>
-      <c r="E41" t="n">
+      <c r="E41" s="4" t="n">
         <v>80</v>
       </c>
-      <c r="F41" t="inlineStr">
+      <c r="F41" s="4" t="inlineStr">
         <is>
           <t>14.25</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="G41" s="4" t="inlineStr">
         <is>
           <t>14.25</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
+      <c r="H41" s="4" t="inlineStr">
         <is>
           <t>3.0769</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
+      <c r="I41" s="4" t="inlineStr">
         <is>
           <t>3.0769</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr">
+      <c r="J41" s="4" t="inlineStr">
         <is>
           <t>3.0769</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr">
+      <c r="K41" s="4" t="inlineStr">
         <is>
           <t>3.0769</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr">
+      <c r="L41" s="4" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="M41" t="inlineStr">
+      <c r="M41" s="4" t="inlineStr">
         <is>
           <t>26.56</t>
         </is>
       </c>
-      <c r="N41" t="inlineStr">
+      <c r="N41" s="4" t="inlineStr">
         <is>
           <t>26.57</t>
         </is>
       </c>
-      <c r="O41" t="inlineStr">
+      <c r="O41" s="4" t="inlineStr">
         <is>
           <t>$61,900.00</t>
         </is>
       </c>
-      <c r="P41" t="inlineStr">
+      <c r="P41" s="4" t="inlineStr">
         <is>
           <t>$29.7596</t>
         </is>
       </c>
-      <c r="Q41" t="inlineStr">
+      <c r="Q41" s="4" t="inlineStr">
         <is>
           <t>$790.41</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
+      <c r="A42" s="4" t="inlineStr">
         <is>
           <t>TRT-0117</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B42" s="4" t="inlineStr">
         <is>
           <t>Belaviv Luk</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C42" s="4" t="inlineStr">
         <is>
           <t>Engineering</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="D42" s="4" t="inlineStr">
         <is>
           <t>03/11/2024</t>
         </is>
       </c>
-      <c r="E42" t="n">
+      <c r="E42" s="4" t="n">
         <v>120</v>
       </c>
-      <c r="F42" t="inlineStr">
+      <c r="F42" s="4" t="inlineStr">
         <is>
           <t>22.00</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
+      <c r="G42" s="4" t="inlineStr">
         <is>
           <t>22.00</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>4.6154</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>4.6154</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>4.6154</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>4.6154</t>
-        </is>
-      </c>
-      <c r="L42" t="inlineStr">
+      <c r="H42" s="4" t="inlineStr">
+        <is>
+          <t>4.6154</t>
+        </is>
+      </c>
+      <c r="I42" s="4" t="inlineStr">
+        <is>
+          <t>4.6154</t>
+        </is>
+      </c>
+      <c r="J42" s="4" t="inlineStr">
+        <is>
+          <t>4.6154</t>
+        </is>
+      </c>
+      <c r="K42" s="4" t="inlineStr">
+        <is>
+          <t>4.6154</t>
+        </is>
+      </c>
+      <c r="L42" s="4" t="inlineStr">
         <is>
           <t>32.00</t>
         </is>
       </c>
-      <c r="M42" t="inlineStr">
+      <c r="M42" s="4" t="inlineStr">
         <is>
           <t>8.46</t>
         </is>
       </c>
-      <c r="N42" t="inlineStr">
+      <c r="N42" s="4" t="inlineStr">
         <is>
           <t>8.48</t>
         </is>
       </c>
-      <c r="O42" t="inlineStr">
+      <c r="O42" s="4" t="inlineStr">
         <is>
           <t>$148,200.00</t>
         </is>
       </c>
-      <c r="P42" t="inlineStr">
+      <c r="P42" s="4" t="inlineStr">
         <is>
           <t>$71.2500</t>
         </is>
       </c>
-      <c r="Q42" t="inlineStr">
+      <c r="Q42" s="4" t="inlineStr">
         <is>
           <t>$602.78</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
+      <c r="A43" s="4" t="inlineStr">
         <is>
           <t>TRT-0119</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B43" s="4" t="inlineStr">
         <is>
           <t>Hectori Bung</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="C43" s="4" t="inlineStr">
         <is>
           <t>Engineering</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="D43" s="4" t="inlineStr">
         <is>
           <t>02/03/2025</t>
         </is>
       </c>
-      <c r="E43" t="n">
+      <c r="E43" s="4" t="n">
         <v>80</v>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="F43" s="4" t="inlineStr">
         <is>
           <t>17.75</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="G43" s="4" t="inlineStr">
         <is>
           <t>17.75</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
+      <c r="H43" s="4" t="inlineStr">
         <is>
           <t>3.0769</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
+      <c r="I43" s="4" t="inlineStr">
         <is>
           <t>3.0769</t>
         </is>
       </c>
-      <c r="J43" t="inlineStr">
+      <c r="J43" s="4" t="inlineStr">
         <is>
           <t>3.0769</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr">
+      <c r="K43" s="4" t="inlineStr">
         <is>
           <t>3.0769</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr">
+      <c r="L43" s="4" t="inlineStr">
         <is>
           <t>8.00</t>
         </is>
       </c>
-      <c r="M43" t="inlineStr">
+      <c r="M43" s="4" t="inlineStr">
         <is>
           <t>22.06</t>
         </is>
       </c>
-      <c r="N43" t="inlineStr">
+      <c r="N43" s="4" t="inlineStr">
         <is>
           <t>22.07</t>
         </is>
       </c>
-      <c r="O43" t="inlineStr">
+      <c r="O43" s="4" t="inlineStr">
         <is>
           <t>$134,000.00</t>
         </is>
       </c>
-      <c r="P43" t="inlineStr">
+      <c r="P43" s="4" t="inlineStr">
         <is>
           <t>$64.4231</t>
         </is>
       </c>
-      <c r="Q43" t="inlineStr">
+      <c r="Q43" s="4" t="inlineStr">
         <is>
           <t>$1,421.17</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
+      <c r="A44" s="4" t="inlineStr">
         <is>
           <t>TRT-0122</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="B44" s="4" t="inlineStr">
         <is>
           <t>Amara Osei-Tutu</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="C44" s="4" t="inlineStr">
         <is>
           <t>Engineering</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="D44" s="4" t="inlineStr">
         <is>
           <t>09/29/2025</t>
         </is>
       </c>
-      <c r="E44" t="n">
+      <c r="E44" s="4" t="n">
         <v>80</v>
       </c>
-      <c r="F44" t="inlineStr">
+      <c r="F44" s="4" t="inlineStr">
         <is>
           <t>19.00</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="G44" s="4" t="inlineStr">
         <is>
           <t>19.00</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
+      <c r="H44" s="4" t="inlineStr">
         <is>
           <t>3.0769</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
+      <c r="I44" s="4" t="inlineStr">
         <is>
           <t>3.0769</t>
         </is>
       </c>
-      <c r="J44" t="inlineStr">
+      <c r="J44" s="4" t="inlineStr">
         <is>
           <t>3.0769</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr">
+      <c r="K44" s="4" t="inlineStr">
         <is>
           <t>3.0769</t>
         </is>
       </c>
-      <c r="L44" t="inlineStr">
+      <c r="L44" s="4" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="M44" t="inlineStr">
+      <c r="M44" s="4" t="inlineStr">
         <is>
           <t>31.31</t>
         </is>
       </c>
-      <c r="N44" t="inlineStr">
+      <c r="N44" s="4" t="inlineStr">
         <is>
           <t>31.32</t>
         </is>
       </c>
-      <c r="O44" t="inlineStr">
+      <c r="O44" s="4" t="inlineStr">
         <is>
           <t>$125,600.00</t>
         </is>
       </c>
-      <c r="P44" t="inlineStr">
+      <c r="P44" s="4" t="inlineStr">
         <is>
           <t>$60.3846</t>
         </is>
       </c>
-      <c r="Q44" t="inlineStr">
+      <c r="Q44" s="4" t="inlineStr">
         <is>
           <t>$1,890.64</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
+      <c r="A45" s="4" t="inlineStr">
         <is>
           <t>TRT-0128</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B45" s="4" t="inlineStr">
         <is>
           <t>Beenan Lanik</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="C45" s="4" t="inlineStr">
         <is>
           <t>Engineering</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="D45" s="4" t="inlineStr">
         <is>
           <t>10/20/2025</t>
         </is>
       </c>
-      <c r="E45" t="n">
+      <c r="E45" s="4" t="n">
         <v>80</v>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="F45" s="4" t="inlineStr">
         <is>
           <t>7.75</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="G45" s="4" t="inlineStr">
         <is>
           <t>7.75</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
+      <c r="H45" s="4" t="inlineStr">
         <is>
           <t>3.0769</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
+      <c r="I45" s="4" t="inlineStr">
         <is>
           <t>3.0769</t>
         </is>
       </c>
-      <c r="J45" t="inlineStr">
+      <c r="J45" s="4" t="inlineStr">
         <is>
           <t>3.0769</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr">
+      <c r="K45" s="4" t="inlineStr">
         <is>
           <t>3.0769</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr">
+      <c r="L45" s="4" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="M45" t="inlineStr">
+      <c r="M45" s="4" t="inlineStr">
         <is>
           <t>20.06</t>
         </is>
       </c>
-      <c r="N45" t="inlineStr">
+      <c r="N45" s="4" t="inlineStr">
         <is>
           <t>20.07</t>
         </is>
       </c>
-      <c r="O45" t="inlineStr">
+      <c r="O45" s="4" t="inlineStr">
         <is>
           <t>$129,750.00</t>
         </is>
       </c>
-      <c r="P45" t="inlineStr">
+      <c r="P45" s="4" t="inlineStr">
         <is>
           <t>$62.3798</t>
         </is>
       </c>
-      <c r="Q45" t="inlineStr">
+      <c r="Q45" s="4" t="inlineStr">
         <is>
           <t>$1,251.34</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
+      <c r="A46" s="4" t="inlineStr">
         <is>
           <t>TRT-0131</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B46" s="4" t="inlineStr">
         <is>
           <t>Aurelio Banda</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="C46" s="4" t="inlineStr">
         <is>
           <t>Marketing</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="D46" s="4" t="inlineStr">
         <is>
           <t>11/10/2025</t>
         </is>
       </c>
-      <c r="E46" t="n">
+      <c r="E46" s="4" t="n">
         <v>80</v>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="F46" s="4" t="inlineStr">
         <is>
           <t>32.00</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
+      <c r="G46" s="4" t="inlineStr">
         <is>
           <t>32.00</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
+      <c r="H46" s="4" t="inlineStr">
         <is>
           <t>3.0769</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
+      <c r="I46" s="4" t="inlineStr">
         <is>
           <t>3.0769</t>
         </is>
       </c>
-      <c r="J46" t="inlineStr">
+      <c r="J46" s="4" t="inlineStr">
         <is>
           <t>3.0769</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr">
+      <c r="K46" s="4" t="inlineStr">
         <is>
           <t>3.0769</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr">
+      <c r="L46" s="4" t="inlineStr">
         <is>
           <t>40.00</t>
         </is>
       </c>
-      <c r="M46" t="inlineStr">
+      <c r="M46" s="4" t="inlineStr">
         <is>
           <t>4.31</t>
         </is>
       </c>
-      <c r="N46" t="inlineStr">
+      <c r="N46" s="4" t="inlineStr">
         <is>
           <t>4.32</t>
         </is>
       </c>
-      <c r="O46" t="inlineStr">
+      <c r="O46" s="4" t="inlineStr">
         <is>
           <t>$76,850.00</t>
         </is>
       </c>
-      <c r="P46" t="inlineStr">
+      <c r="P46" s="4" t="inlineStr">
         <is>
           <t>$36.9471</t>
         </is>
       </c>
-      <c r="Q46" t="inlineStr">
+      <c r="Q46" s="4" t="inlineStr">
         <is>
           <t>$159.24</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
+      <c r="A47" s="4" t="inlineStr">
         <is>
           <t>TRT-0135</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="B47" s="4" t="inlineStr">
         <is>
           <t>Solveig Okonjo</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C47" s="4" t="inlineStr">
         <is>
           <t>Customer Success</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="D47" s="4" t="inlineStr">
         <is>
           <t>12/01/2025</t>
         </is>
       </c>
-      <c r="E47" t="n">
+      <c r="E47" s="4" t="n">
         <v>80</v>
       </c>
-      <c r="F47" t="inlineStr">
+      <c r="F47" s="4" t="inlineStr">
         <is>
           <t>37.00</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
+      <c r="G47" s="4" t="inlineStr">
         <is>
           <t>37.00</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
+      <c r="H47" s="4" t="inlineStr">
         <is>
           <t>3.0769</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
+      <c r="I47" s="4" t="inlineStr">
         <is>
           <t>3.0769</t>
         </is>
       </c>
-      <c r="J47" t="inlineStr">
+      <c r="J47" s="4" t="inlineStr">
         <is>
           <t>3.0769</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr">
+      <c r="K47" s="4" t="inlineStr">
         <is>
           <t>3.0769</t>
         </is>
       </c>
-      <c r="L47" t="inlineStr">
+      <c r="L47" s="4" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="M47" t="inlineStr">
+      <c r="M47" s="4" t="inlineStr">
         <is>
           <t>49.31</t>
         </is>
       </c>
-      <c r="N47" t="inlineStr">
+      <c r="N47" s="4" t="inlineStr">
         <is>
           <t>49.32</t>
         </is>
       </c>
-      <c r="O47" t="inlineStr">
+      <c r="O47" s="4" t="inlineStr">
         <is>
           <t>$94,600.00</t>
         </is>
       </c>
-      <c r="P47" t="inlineStr">
+      <c r="P47" s="4" t="inlineStr">
         <is>
           <t>$45.4808</t>
         </is>
       </c>
-      <c r="Q47" t="inlineStr">
+      <c r="Q47" s="4" t="inlineStr">
         <is>
           <t>$2,242.66</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
+      <c r="A48" s="4" t="inlineStr">
         <is>
           <t>TRT-0141</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="B48" s="4" t="inlineStr">
         <is>
           <t>Beatriz Quintanilla</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="C48" s="4" t="inlineStr">
         <is>
           <t>Customer Success</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="D48" s="4" t="inlineStr">
         <is>
           <t>11/03/2025</t>
         </is>
       </c>
-      <c r="E48" t="n">
+      <c r="E48" s="4" t="n">
         <v>80</v>
       </c>
-      <c r="F48" t="inlineStr">
+      <c r="F48" s="4" t="inlineStr">
         <is>
           <t>20.75</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
+      <c r="G48" s="4" t="inlineStr">
         <is>
           <t>20.75</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
+      <c r="H48" s="4" t="inlineStr">
         <is>
           <t>1.9231</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
+      <c r="I48" s="4" t="inlineStr">
         <is>
           <t>1.9231</t>
         </is>
       </c>
-      <c r="J48" t="inlineStr">
+      <c r="J48" s="4" t="inlineStr">
         <is>
           <t>1.9231</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr">
+      <c r="K48" s="4" t="inlineStr">
         <is>
           <t>3.0769</t>
         </is>
       </c>
-      <c r="L48" t="inlineStr">
+      <c r="L48" s="4" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="M48" t="inlineStr">
+      <c r="M48" s="4" t="inlineStr">
         <is>
           <t>29.60</t>
         </is>
       </c>
-      <c r="N48" t="inlineStr">
+      <c r="N48" s="4" t="inlineStr">
         <is>
           <t>29.59</t>
         </is>
       </c>
-      <c r="O48" t="inlineStr">
+      <c r="O48" s="4" t="inlineStr">
         <is>
           <t>$47,840.00</t>
         </is>
       </c>
-      <c r="P48" t="inlineStr">
+      <c r="P48" s="4" t="inlineStr">
         <is>
           <t>$23.0000</t>
         </is>
       </c>
-      <c r="Q48" t="inlineStr">
+      <c r="Q48" s="4" t="inlineStr">
         <is>
           <t>$680.80</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
+      <c r="A49" s="4" t="inlineStr">
         <is>
           <t>TRT-0150</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="B49" s="4" t="inlineStr">
         <is>
           <t>Ingra Zolberg</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="C49" s="4" t="inlineStr">
         <is>
           <t>Marketing</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="D49" s="4" t="inlineStr">
         <is>
           <t>07/01/2026</t>
         </is>
       </c>
-      <c r="E49" t="n">
+      <c r="E49" s="4" t="n">
         <v>80</v>
       </c>
-      <c r="F49" t="inlineStr">
+      <c r="F49" s="4" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
+      <c r="G49" s="4" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
+      <c r="H49" s="4" t="inlineStr">
         <is>
           <t>3.0769</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
+      <c r="I49" s="4" t="inlineStr">
         <is>
           <t>3.0769</t>
         </is>
       </c>
-      <c r="J49" t="inlineStr">
+      <c r="J49" s="4" t="inlineStr">
         <is>
           <t>3.0769</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr">
+      <c r="K49" s="4" t="inlineStr">
         <is>
           <t>3.0769</t>
         </is>
       </c>
-      <c r="L49" t="inlineStr">
+      <c r="L49" s="4" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="M49" t="inlineStr">
+      <c r="M49" s="4" t="inlineStr">
         <is>
           <t>12.31</t>
         </is>
       </c>
-      <c r="N49" t="inlineStr">
+      <c r="N49" s="4" t="inlineStr">
         <is>
           <t>12.32</t>
         </is>
       </c>
-      <c r="O49" t="inlineStr">
+      <c r="O49" s="4" t="inlineStr">
         <is>
           <t>$62,450.00</t>
         </is>
       </c>
-      <c r="P49" t="inlineStr">
+      <c r="P49" s="4" t="inlineStr">
         <is>
           <t>$30.0240</t>
         </is>
       </c>
-      <c r="Q49" t="inlineStr">
+      <c r="Q49" s="4" t="inlineStr">
         <is>
           <t>$369.60</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
+      <c r="A50" s="4" t="inlineStr">
         <is>
           <t>TRT-0153</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="B50" s="4" t="inlineStr">
         <is>
           <t>Simone Okonkwo</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="C50" s="4" t="inlineStr">
         <is>
           <t>Customer Success</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
+      <c r="D50" s="4" t="inlineStr">
         <is>
           <t>07/22/2026</t>
         </is>
       </c>
-      <c r="E50" t="n">
+      <c r="E50" s="4" t="n">
         <v>80</v>
       </c>
-      <c r="F50" t="inlineStr">
+      <c r="F50" s="4" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
+      <c r="G50" s="4" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
+      <c r="H50" s="4" t="inlineStr">
         <is>
           <t>0.0000</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
+      <c r="I50" s="4" t="inlineStr">
         <is>
           <t>0.0000</t>
         </is>
       </c>
-      <c r="J50" t="inlineStr">
+      <c r="J50" s="4" t="inlineStr">
         <is>
           <t>3.0769</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr">
+      <c r="K50" s="4" t="inlineStr">
         <is>
           <t>3.0769</t>
         </is>
       </c>
-      <c r="L50" t="inlineStr">
+      <c r="L50" s="4" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="M50" t="inlineStr">
+      <c r="M50" s="4" t="inlineStr">
         <is>
           <t>6.15</t>
         </is>
       </c>
-      <c r="N50" t="inlineStr">
+      <c r="N50" s="4" t="inlineStr">
         <is>
           <t>6.16</t>
         </is>
       </c>
-      <c r="O50" t="inlineStr">
+      <c r="O50" s="4" t="inlineStr">
         <is>
           <t>$92,000.00</t>
         </is>
       </c>
-      <c r="P50" t="inlineStr">
+      <c r="P50" s="4" t="inlineStr">
         <is>
           <t>$44.2308</t>
         </is>
       </c>
-      <c r="Q50" t="inlineStr">
+      <c r="Q50" s="4" t="inlineStr">
         <is>
           <t>$272.02</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr">
+      <c r="A51" s="4" t="inlineStr">
         <is>
           <t>TRT-0154</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="B51" s="4" t="inlineStr">
         <is>
           <t>Anjelina Brocollini</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="C51" s="4" t="inlineStr">
         <is>
           <t>Finance and Corporate</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
+      <c r="D51" s="4" t="inlineStr">
         <is>
           <t>08/03/2026</t>
         </is>
       </c>
-      <c r="E51" t="n">
+      <c r="E51" s="4" t="n">
         <v>80</v>
       </c>
-      <c r="F51" t="inlineStr">
+      <c r="F51" s="4" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
+      <c r="G51" s="4" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
+      <c r="H51" s="4" t="inlineStr">
         <is>
           <t>0.0000</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
+      <c r="I51" s="4" t="inlineStr">
         <is>
           <t>0.0000</t>
         </is>
       </c>
-      <c r="J51" t="inlineStr">
+      <c r="J51" s="4" t="inlineStr">
         <is>
           <t>0.0000</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr">
+      <c r="K51" s="4" t="inlineStr">
         <is>
           <t>3.0769</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr">
+      <c r="L51" s="4" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="M51" t="inlineStr">
+      <c r="M51" s="4" t="inlineStr">
         <is>
           <t>3.08</t>
         </is>
       </c>
-      <c r="N51" t="inlineStr">
+      <c r="N51" s="4" t="inlineStr">
         <is>
           <t>3.08</t>
         </is>
       </c>
-      <c r="O51" t="inlineStr">
+      <c r="O51" s="4" t="inlineStr">
         <is>
           <t>$172,500.00</t>
         </is>
       </c>
-      <c r="P51" t="inlineStr">
+      <c r="P51" s="4" t="inlineStr">
         <is>
           <t>$82.9327</t>
         </is>
       </c>
-      <c r="Q51" t="inlineStr">
+      <c r="Q51" s="4" t="inlineStr">
         <is>
           <t>$255.43</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr">
+      <c r="A52" s="4" t="inlineStr">
         <is>
           <t>TRT-0155</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="B52" s="4" t="inlineStr">
         <is>
           <t>Rafael Ibarra</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
+      <c r="C52" s="4" t="inlineStr">
         <is>
           <t>Sales</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
+      <c r="D52" s="4" t="inlineStr">
         <is>
           <t>08/03/2026</t>
         </is>
       </c>
-      <c r="E52" t="n">
+      <c r="E52" s="4" t="n">
         <v>80</v>
       </c>
-      <c r="F52" t="inlineStr">
+      <c r="F52" s="4" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr">
+      <c r="G52" s="4" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
+      <c r="H52" s="4" t="inlineStr">
         <is>
           <t>0.0000</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
+      <c r="I52" s="4" t="inlineStr">
         <is>
           <t>0.0000</t>
         </is>
       </c>
-      <c r="J52" t="inlineStr">
+      <c r="J52" s="4" t="inlineStr">
         <is>
           <t>0.0000</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr">
+      <c r="K52" s="4" t="inlineStr">
         <is>
           <t>3.0769</t>
         </is>
       </c>
-      <c r="L52" t="inlineStr">
+      <c r="L52" s="4" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="M52" t="inlineStr">
+      <c r="M52" s="4" t="inlineStr">
         <is>
           <t>3.08</t>
         </is>
       </c>
-      <c r="N52" t="inlineStr">
+      <c r="N52" s="4" t="inlineStr">
         <is>
           <t>3.08</t>
         </is>
       </c>
-      <c r="O52" t="inlineStr">
+      <c r="O52" s="4" t="inlineStr">
         <is>
           <t>$56,300.00</t>
         </is>
       </c>
-      <c r="P52" t="inlineStr">
+      <c r="P52" s="4" t="inlineStr">
         <is>
           <t>$27.0673</t>
         </is>
       </c>
-      <c r="Q52" t="inlineStr">
+      <c r="Q52" s="4" t="inlineStr">
         <is>
           <t>$83.37</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr">
+      <c r="A53" s="4" t="inlineStr">
         <is>
           <t>TRT-0156</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="B53" s="4" t="inlineStr">
         <is>
           <t>Casey Ouk</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
+      <c r="C53" s="4" t="inlineStr">
         <is>
           <t>Finance and Corporate</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
+      <c r="D53" s="4" t="inlineStr">
         <is>
           <t>08/17/2026</t>
         </is>
       </c>
-      <c r="E53" t="n">
+      <c r="E53" s="4" t="n">
         <v>80</v>
       </c>
-      <c r="F53" t="inlineStr">
+      <c r="F53" s="4" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
+      <c r="G53" s="4" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
+      <c r="H53" s="4" t="inlineStr">
         <is>
           <t>0.0000</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
+      <c r="I53" s="4" t="inlineStr">
         <is>
           <t>0.0000</t>
         </is>
       </c>
-      <c r="J53" t="inlineStr">
+      <c r="J53" s="4" t="inlineStr">
         <is>
           <t>0.0000</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr">
+      <c r="K53" s="4" t="inlineStr">
         <is>
           <t>0.0000</t>
         </is>
       </c>
-      <c r="L53" t="inlineStr">
+      <c r="L53" s="4" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="M53" t="inlineStr">
+      <c r="M53" s="4" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="N53" t="inlineStr">
+      <c r="N53" s="4" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="O53" t="inlineStr">
+      <c r="O53" s="4" t="inlineStr">
         <is>
           <t>$71,900.00</t>
         </is>
       </c>
-      <c r="P53" t="inlineStr">
+      <c r="P53" s="4" t="inlineStr">
         <is>
           <t>$34.5673</t>
         </is>
       </c>
-      <c r="Q53" t="inlineStr">
+      <c r="Q53" s="4" t="inlineStr">
         <is>
           <t>$0.00</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr">
+      <c r="A54" s="4" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr"/>
-      <c r="C54" t="inlineStr"/>
-      <c r="D54" t="inlineStr"/>
-      <c r="E54" t="inlineStr"/>
-      <c r="F54" t="inlineStr"/>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
+      <c r="B54" s="4" t="inlineStr"/>
+      <c r="C54" s="4" t="inlineStr"/>
+      <c r="D54" s="4" t="inlineStr"/>
+      <c r="E54" s="4" t="inlineStr"/>
+      <c r="F54" s="4" t="inlineStr"/>
+      <c r="G54" s="4" t="inlineStr"/>
+      <c r="H54" s="4" t="inlineStr"/>
+      <c r="I54" s="4" t="inlineStr"/>
+      <c r="J54" s="4" t="inlineStr"/>
+      <c r="K54" s="4" t="inlineStr"/>
+      <c r="L54" s="4" t="inlineStr"/>
+      <c r="M54" s="4" t="inlineStr">
         <is>
           <t>1,522.17</t>
         </is>
       </c>
-      <c r="N54" t="inlineStr"/>
-      <c r="O54" t="inlineStr"/>
-      <c r="P54" t="inlineStr"/>
-      <c r="Q54" t="inlineStr">
+      <c r="N54" s="4" t="inlineStr"/>
+      <c r="O54" s="4" t="inlineStr"/>
+      <c r="P54" s="4" t="inlineStr"/>
+      <c r="Q54" s="4" t="inlineStr">
         <is>
           <t>$92,739.54</t>
         </is>

--- a/tasks/HR_Troutly_T2_pto_liability_close/03_show_your_work.xlsx
+++ b/tasks/HR_Troutly_T2_pto_liability_close/03_show_your_work.xlsx
@@ -469,7 +469,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Biweekly accrual at the annual tier over 26, posted on the pay date; carryover capped at 40.0 hours at 06/30/2026; tiers by adjusted service date, the change in the period containing the anniversary; valued at the rate on file over 2,080; ended employees out; wiki pages do not set policy.</t>
+          <t>Biweekly accrual at the annual tier over 26, posted on the pay date. Carryover capped at 40.0 hours at 06/30/2026. Tiers by adjusted service date, the change in the period containing the anniversary. Valued at the rate on file over 2,080. Ended employees out. Wiki pages do not set policy.</t>
         </is>
       </c>
     </row>
@@ -486,7 +486,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Section 7 incorporates the memo; 2.2 part-time accrual pro-rata under 30 hours; 7.6 service bridges on a break under 365 days; 5.4 the $3,000.00 Support Specialist step; 3.2 the signed document over the record; 7.3 totals are the sum of the rounded rows.</t>
+          <t>Section 7 incorporates the memo. 2.2 accrues part-time pro-rata under 30 hours. 7.6 bridges service on a break under 365 days. 5.4 carries the $3,000.00 Support Specialist step. 3.2 puts the signed document over the record. 7.3 totals the rounded rows.</t>
         </is>
       </c>
     </row>
@@ -520,7 +520,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>52 active employees. BambooHR carries 57 active rows: four contractors, three employees whose employment ended 03/20, 05/08 and 06/15/2026, and no row for TRT-0153 and TRT-0155, Never Loaded on the crosswalk.</t>
+          <t>52 active employees. BambooHR carries 57 active rows. Four are contractors, three are employees whose employment ended 03/20, 05/08 and 06/15/2026, and TRT-0153 and TRT-0155 have no row, Never Loaded on the crosswalk.</t>
         </is>
       </c>
     </row>
@@ -537,7 +537,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>51 balances at 06/30/2026; eleven above 40.0 hours, TRT-0005 at 92.50 the highest. The HRIS report, the load file and the July close carry them uncapped.</t>
+          <t>51 balances at 06/30/2026. Eleven are above 40.0 hours, TRT-0005 at 92.50 the highest. The HRIS report, the load file and the July close carry them uncapped.</t>
         </is>
       </c>
     </row>
@@ -554,7 +554,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Pay dates 07/10/2026, 07/24/2026, 08/07/2026 and 08/21/2026, posted by 08/31/2026; 09/04/2026 is the fifth and is not posted.</t>
+          <t>Pay dates 07/10/2026, 07/24/2026, 08/07/2026 and 08/21/2026, posted by 08/31/2026. The fifth pays 09/04/2026 and is not posted.</t>
         </is>
       </c>
     </row>
@@ -571,7 +571,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Nine migrated records read 07/01/2026 in BambooHR and on the roster and carry their true dates in the archive and the letters. TRT-0071 hired 03/08/2021, ended 08/25/2023, rehired 04/22/2024: a break under 365 days, bridged under handbook 7.6.</t>
+          <t>Nine migrated records read 07/01/2026 in BambooHR and on the roster and carry their true dates in the archive and the letters. TRT-0071 was hired 03/08/2021, ended 08/25/2023 and was rehired 04/22/2024, a break under 365 days, bridged under handbook 7.6.</t>
         </is>
       </c>
     </row>
@@ -588,7 +588,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>TRT-0018 reaches five years inside the fourth period: three periods at 120 and one at 160, 20.0000 hours accrued.</t>
+          <t>TRT-0018 reaches five years inside the fourth period. Three periods at 120 and one at 160, 20.0000 hours accrued.</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>TRT-0096 steps $3,000.00 on her 08/17/2026 anniversary: $61,000.00 on file at 08/31/2026.</t>
+          <t>TRT-0096 steps $3,000.00 on her 08/17/2026 anniversary to $61,000.00 on file at 08/31/2026.</t>
         </is>
       </c>
     </row>
@@ -639,7 +639,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>25 hours to 32 hours effective 08/10/2026; pro-rata under 30 hours, so three periods at 25 and one at 32.</t>
+          <t>25 hours to 32 hours effective 08/10/2026. Pro-rata under 30 hours, so three periods at 25 and one at 32.</t>
         </is>
       </c>
     </row>
@@ -656,7 +656,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Okonkwo started 07/22/2026 at $92,000.00, moved from 07/13/2026 by the thread of 07/09/2026; Ibarra 08/03/2026 at $56,300.00. Both accrue at 80 from the period containing the start, as BambooHR credited TRT-0150: 6.15 and 3.08 hours.</t>
+          <t>Okonkwo started 07/22/2026 at $92,000.00, moved from 07/13/2026 by the thread of 07/09/2026. Ibarra started 08/03/2026 at $56,300.00. Both accrue at 80 from the period containing the start, as BambooHR credited TRT-0150, 6.15 and 3.08 hours.</t>
         </is>
       </c>
     </row>
@@ -673,7 +673,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>24 approved requests, 560.00 hours, all in July; TRT-0001 40.00 hours.</t>
+          <t>24 approved requests, 560.00 hours, all in July. TRT-0001 used 40.00 hours.</t>
         </is>
       </c>
     </row>
@@ -690,7 +690,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>The requester's method: the HRIS balance, tier and rate per row, three ended employees inside, $90,862.13 booked.</t>
+          <t>The requester's method. The HRIS balance, tier and rate per row, three ended employees inside, $90,862.13 booked.</t>
         </is>
       </c>
     </row>
@@ -1257,7 +1257,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>The determination carries 75 of 92 points; the gate is the total. Every row is read from the Wiki.js pages table or the BambooHR tables.</t>
+          <t>The determination carries 75 of 92 points and the gate is the total. Every row is read from the Wiki.js pages table or the BambooHR tables.</t>
         </is>
       </c>
       <c r="C24" s="2" t="n"/>
@@ -1302,7 +1302,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>52 from the roster and the org chart: BambooHR's 57 active less four contractors less three ended plus the two unloaded hires.</t>
+          <t>52 from the roster and the org chart. BambooHR's 57 active less four contractors less three ended plus the two unloaded hires.</t>
         </is>
       </c>
     </row>
@@ -1314,7 +1314,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>The cutover memo over the 2025 policy and the wiki page; the handbook's bridging, part-time, step and signed-document rules.</t>
+          <t>The cutover memo over the 2025 policy and the wiki page. The handbook's bridging, part-time, step and signed-document rules.</t>
         </is>
       </c>
     </row>
@@ -1326,7 +1326,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>The archive's 06/30/2026 balance capped at 40.00; eleven capped; the two hires at 0.00.</t>
+          <t>The archive's 06/30/2026 balance capped at 40.00. Eleven capped. The two hires at 0.00.</t>
         </is>
       </c>
     </row>
@@ -1338,7 +1338,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>The archive's and the letters' dates over the loaded 07/01/2026; TRT-0071 bridged to 03/08/2021 at 160; five migrated records at 120; TRT-0018 to 160 in the fourth period.</t>
+          <t>The archive's and the letters' dates over the loaded 07/01/2026. TRT-0071 bridged to 03/08/2021 at 160. Five migrated records at 120. TRT-0018 to 160 in the fourth period.</t>
         </is>
       </c>
     </row>
@@ -1350,7 +1350,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Four posted periods at the tier over 26 to four decimals, the period containing a start credited in full; TRT-0141 pro-rata at 25 then 32 hours.</t>
+          <t>Four posted periods at the tier over 26 to four decimals, the period containing a start credited in full. TRT-0141 pro-rata at 25 then 32 hours.</t>
         </is>
       </c>
     </row>
@@ -1374,7 +1374,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>The rate on file over 2,080 to four decimals: TRT-0088 at $118,000.00, TRT-0117 at $148,200.00 and TRT-0096 at $61,000.00 by the signed documents and the step.</t>
+          <t>The rate on file over 2,080 to four decimals. TRT-0088 at $118,000.00, TRT-0117 at $148,200.00 and TRT-0096 at $61,000.00 by the signed documents and the step.</t>
         </is>
       </c>
     </row>
@@ -1386,7 +1386,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Balance to two decimals, liability to the cent, the total the sum of the rounded rows: 1,522.17 hours and $92,739.54, $92,772.88 under posted rounding.</t>
+          <t>Balance to two decimals, liability to the cent, the total the sum of the rounded rows. 1,522.17 hours and $92,739.54, $92,772.88 under posted rounding.</t>
         </is>
       </c>
     </row>
@@ -1398,7 +1398,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>PTO Liability - 08/31/2026: the summary above the table, seven columns, 52 rows keyed by ID, published.</t>
+          <t>PTO Liability - 08/31/2026. The summary above the table, seven columns, 52 rows keyed by ID, published.</t>
         </is>
       </c>
     </row>

--- a/tasks/HR_Troutly_T2_pto_liability_close/03_show_your_work.xlsx
+++ b/tasks/HR_Troutly_T2_pto_liability_close/03_show_your_work.xlsx
@@ -722,14 +722,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E24"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="110" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -745,15 +744,10 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Family</t>
+          <t>Weight</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Weight</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Gate</t>
         </is>
@@ -768,15 +762,10 @@
           <t>States that a Wiki.js page titled PTO Liability - 08/31/2026 is published.</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>The page and its form</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="n">
+      <c r="C2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -791,15 +780,10 @@
           <t>States, on the PTO liability page, the 52 current employees at 08/31/2026 as the only employee rows.</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>The page and its form</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="n">
+      <c r="C3" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -814,15 +798,10 @@
           <t>States, on the PTO liability page, hours to two decimals, hourly rates to four decimals, dollars to the cent and a total equal to the sum of the rows.</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>The page and its form</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="n">
+      <c r="C4" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -837,15 +816,10 @@
           <t>States, on the PTO liability page, a summary with the employee count, the total hours and the total dollar liability.</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>The page and its form</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="n">
+      <c r="C5" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -860,15 +834,10 @@
           <t>States, on the PTO liability page, a total dollar liability of $92,739.54.</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>The determination</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="C6" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Critical value</t>
         </is>
@@ -883,15 +852,10 @@
           <t>States, on the PTO liability page, an opening balance of 40.00 hours for each of the 11 employees whose 06/30/2026 balance exceeded 40.0 hours.</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>The determination</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="n">
+      <c r="C7" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -906,15 +870,10 @@
           <t>States, on the PTO liability page, the 120-hour tier for TRT-0043, TRT-0051, TRT-0058, TRT-0079 and TRT-0083.</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>The determination</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="n">
+      <c r="C8" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -929,15 +888,10 @@
           <t>States, on the PTO liability page, the 160-hour tier for Samuel Burkenham, TRT-0071, with service bridged to 03/08/2021.</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>The determination</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="n">
+      <c r="C9" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -952,15 +906,10 @@
           <t>States, on the PTO liability page, an accrual of 20.0000 hours for Marisela Thornbury, TRT-0018, three periods at the 120-hour tier and one at 160.</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>The determination</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="n">
+      <c r="C10" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -975,15 +924,10 @@
           <t>States, on the PTO liability page, an hourly rate of $56.7308 for Yolanda Featherstone, TRT-0088.</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>The determination</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="n">
+      <c r="C11" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -998,15 +942,10 @@
           <t>States, on the PTO liability page, an hourly rate of $71.2500 for Belaviv Luk, TRT-0117.</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>The determination</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="n">
+      <c r="C12" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1021,15 +960,10 @@
           <t>States, on the PTO liability page, an hourly rate of $29.3269 for Delphine Marchetti, TRT-0096.</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>The determination</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="n">
+      <c r="C13" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1044,15 +978,10 @@
           <t>States, on the PTO liability page, a balance of 29.60 hours for Beatriz Quintanilla, TRT-0141.</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>The determination</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="n">
+      <c r="C14" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1067,15 +996,10 @@
           <t>States, on the PTO liability page, no contractor row, CTR-2001 to CTR-2004.</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>The determination</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="n">
+      <c r="C15" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1090,15 +1014,10 @@
           <t>States, on the PTO liability page, no row for TRT-0037, TRT-0049, TRT-0064 or TRT-0006.</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>The determination</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="n">
+      <c r="C16" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1113,15 +1032,10 @@
           <t>States, on the PTO liability page, Simone Okonkwo, TRT-0153, and Rafael Ibarra, TRT-0155, at the 80-hour tier with accruals since their start dates.</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>The determination</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="n">
+      <c r="C17" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1136,15 +1050,10 @@
           <t>States, on the PTO liability page, a balance of 62.62 hours for Sora Jackson, TRT-0002, four posted periods at the 160-hour tier.</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>The determination</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="n">
+      <c r="C18" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1159,15 +1068,10 @@
           <t>States, on the PTO liability page, a balance of 22.87 hours for Michael Labeson, TRT-0001, with 40.00 hours of approved time off deducted.</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>The determination</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="n">
+      <c r="C19" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1182,15 +1086,10 @@
           <t>States, in BambooHR, the PTO policy the schedule's tier gives for each of the 6 employees whose loaded policy differed.</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>BambooHR brought to the schedule</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="n">
+      <c r="C20" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1205,15 +1104,10 @@
           <t>States, in BambooHR, a PTO balance equal to the schedule's 08/31/2026 balance for every employee on the schedule.</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>BambooHR brought to the schedule</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="n">
+      <c r="C21" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1228,15 +1122,10 @@
           <t>States, in BambooHR, a PTO balance row for TRT-0153 and TRT-0155.</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>BambooHR brought to the schedule</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="n">
+      <c r="C22" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1247,7 +1136,6 @@
       <c r="B23" s="2" t="n"/>
       <c r="C23" s="2" t="n"/>
       <c r="D23" s="2" t="n"/>
-      <c r="E23" s="2" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -1257,12 +1145,11 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>The determination carries 75 of 92 points and the gate is the total. Every row is read from the Wiki.js pages table or the BambooHR tables.</t>
+          <t>The determination carries 70 of 87 points and the gate is the total. Every row is read from the Wiki.js pages table or the BambooHR tables.</t>
         </is>
       </c>
       <c r="C24" s="2" t="n"/>
       <c r="D24" s="2" t="n"/>
-      <c r="E24" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/tasks/HR_Troutly_T2_pto_liability_close/03_show_your_work.xlsx
+++ b/tasks/HR_Troutly_T2_pto_liability_close/03_show_your_work.xlsx
@@ -849,7 +849,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>States, on the PTO liability page, an opening balance of 40.00 hours for each of the 11 employees whose 06/30/2026 balance exceeded 40.0 hours.</t>
+          <t>States, on the PTO liability page, balances of 64.62, 64.62, 58.46, 58.46 and 58.46 hours for TRT-0005, TRT-0009, TRT-0014, TRT-0023 and TRT-0040, the five above 40.0 hours at 06/30/2026 whose balance the cap alone moves.</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">

--- a/tasks/HR_Troutly_T2_pto_liability_close/03_show_your_work.xlsx
+++ b/tasks/HR_Troutly_T2_pto_liability_close/03_show_your_work.xlsx
@@ -722,7 +722,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1150,6 +1150,62 @@
       </c>
       <c r="C24" s="2" t="n"/>
       <c r="D24" s="2" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Each row grades a rule, and the rule is what a group of cells has in common. A wrong cell is never graded as a wrong cell. It is graded as the rule the run failed to apply, once.</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="n"/>
+      <c r="D25" s="2" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>The gate grades every rule at once through the total, the one number all 364 cells feed. Under the one-cent rule it equals the schedule's only if all 52 liabilities are right.</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="n"/>
+      <c r="D26" s="2" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>Rows 6 to 13 each grade one rule on the cells where only that rule moves the value. Rows 2, 14, 15 and 16 grade the population on the set of IDs. Rows 19 to 21 grade BambooHR on its tables.</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="n"/>
+      <c r="D27" s="2" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Drop one rule and one more row fails. The registered paths in 02_task_metadata.md are the proof.</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="n"/>
+      <c r="D28" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/tasks/HR_Troutly_T2_pto_liability_close/03_show_your_work.xlsx
+++ b/tasks/HR_Troutly_T2_pto_liability_close/03_show_your_work.xlsx
@@ -1159,7 +1159,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Each row grades a rule, and the rule is what a group of cells has in common. A wrong cell is never graded as a wrong cell. It is graded as the rule the run failed to apply, once.</t>
+          <t>Each row grades the correct application of one rule across the group of employees it governs, by reading a total over the group. A total moves if any single entry under it is wrong, so one wrong cell fails the rule once and never twice.</t>
         </is>
       </c>
       <c r="C25" s="2" t="n"/>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>The gate grades every rule at once through the total, the one number all 364 cells feed. Under the one-cent rule it equals the schedule's only if all 52 liabilities are right.</t>
+          <t>The gate reads the total of all 52 liabilities, the one number all 364 cells feed. Under the one-cent rule it equals the schedule's only if every entry is right. The witness rows read the cells of the employees their rule alone moves.</t>
         </is>
       </c>
       <c r="C26" s="2" t="n"/>

--- a/tasks/HR_Troutly_T2_pto_liability_close/03_show_your_work.xlsx
+++ b/tasks/HR_Troutly_T2_pto_liability_close/03_show_your_work.xlsx
@@ -1173,7 +1173,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>The gate reads the total of all 52 liabilities, the one number all 364 cells feed. Under the one-cent rule it equals the schedule's only if every entry is right. The witness rows read the cells of the employees their rule alone moves.</t>
+          <t>The gate reads the total of all 52 liabilities, the one number all 364 cells feed. The reviewer rules allow it one cent of tolerance, and it matches the schedule's within that only if every entry is right. The witness rows read the cells of the employees their rule alone moves.</t>
         </is>
       </c>
       <c r="C26" s="2" t="n"/>

--- a/tasks/HR_Troutly_T2_pto_liability_close/03_show_your_work.xlsx
+++ b/tasks/HR_Troutly_T2_pto_liability_close/03_show_your_work.xlsx
@@ -1159,7 +1159,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Each row grades the correct application of one rule across the group of employees it governs, by reading a total over the group. A total moves if any single entry under it is wrong, so one wrong cell fails the rule once and never twice.</t>
+          <t>The gate grades every rule across the whole group at once. It reads the total of all 52 liabilities, the one number all 364 cells feed. The reviewer rules allow it one cent of tolerance, and it matches the schedule's within that only if every entry is right.</t>
         </is>
       </c>
       <c r="C25" s="2" t="n"/>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>The gate reads the total of all 52 liabilities, the one number all 364 cells feed. The reviewer rules allow it one cent of tolerance, and it matches the schedule's within that only if every entry is right. The witness rows read the cells of the employees their rule alone moves.</t>
+          <t>Each witness row grades one rule on the employees that rule alone moves, so one wrong cell fails a rule once and never twice. Where the rule touches many, the row reads a group, the five capped or the five loaded tiers. Where the world applies it to one person, the bridge, the anniversary, the step and the part-time schedule, the row reads that person. Where it touches everyone, the periods and the usage, one clean witness proves the application.</t>
         </is>
       </c>
       <c r="C26" s="2" t="n"/>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Rows 6 to 13 each grade one rule on the cells where only that rule moves the value. Rows 2, 14, 15 and 16 grade the population on the set of IDs. Rows 19 to 21 grade BambooHR on its tables.</t>
+          <t>Rows 2, 14, 15 and 16 grade the population on the set of IDs. Rows 19 to 21 grade BambooHR on its tables.</t>
         </is>
       </c>
       <c r="C27" s="2" t="n"/>

--- a/tasks/HR_Troutly_T2_pto_liability_close/03_show_your_work.xlsx
+++ b/tasks/HR_Troutly_T2_pto_liability_close/03_show_your_work.xlsx
@@ -722,7 +722,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D28"/>
+  <dimension ref="A1:D26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>The determination carries 70 of 87 points and the gate is the total. Every row is read from the Wiki.js pages table or the BambooHR tables.</t>
+          <t>The gate grades every rule across the whole group at once. It reads the total of all 52 liabilities, the one number all 364 cells feed, and it matches the schedule's only if every entry is right.</t>
         </is>
       </c>
       <c r="C24" s="2" t="n"/>
@@ -1159,7 +1159,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>The gate grades every rule across the whole group at once. It reads the total of all 52 liabilities, the one number all 364 cells feed. The reviewer rules allow it one cent of tolerance, and it matches the schedule's within that only if every entry is right.</t>
+          <t>Each witness row grades one rule on the employees that rule alone moves, so one wrong cell fails a rule once and never twice. Where the rule touches many, the row reads a group, the five capped or the five loaded tiers. Where the world applies it to one person, the bridge, the anniversary, the step and the part-time schedule, the row reads that person. Where it touches everyone, the periods and the usage, one clean witness proves the application.</t>
         </is>
       </c>
       <c r="C25" s="2" t="n"/>
@@ -1173,39 +1173,11 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Each witness row grades one rule on the employees that rule alone moves, so one wrong cell fails a rule once and never twice. Where the rule touches many, the row reads a group, the five capped or the five loaded tiers. Where the world applies it to one person, the bridge, the anniversary, the step and the part-time schedule, the row reads that person. Where it touches everyone, the periods and the usage, one clean witness proves the application.</t>
+          <t>Rows 2, 14, 15 and 16 grade the population on the set of IDs. Rows 19 to 21 grade BambooHR on its tables.</t>
         </is>
       </c>
       <c r="C26" s="2" t="n"/>
       <c r="D26" s="2" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>Note</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>Rows 2, 14, 15 and 16 grade the population on the set of IDs. Rows 19 to 21 grade BambooHR on its tables.</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="n"/>
-      <c r="D27" s="2" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>Note</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>Drop one rule and one more row fails. The registered paths in 02_task_metadata.md are the proof.</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="n"/>
-      <c r="D28" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/tasks/HR_Troutly_T2_pto_liability_close/03_show_your_work.xlsx
+++ b/tasks/HR_Troutly_T2_pto_liability_close/03_show_your_work.xlsx
@@ -1159,7 +1159,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Each witness row grades one rule on the employees that rule alone moves, so one wrong cell fails a rule once and never twice. Where the rule touches many, the row reads a group, the five capped or the five loaded tiers. Where the world applies it to one person, the bridge, the anniversary, the step and the part-time schedule, the row reads that person. Where it touches everyone, the periods and the usage, one clean witness proves the application.</t>
+          <t>Each witness row grades one rule on the employees that rule alone moves, so one wrong cell fails a rule once and never twice. Where the rule touches many, the row reads a group, the five capped or the five loaded tiers. Where the world applies it to one person, the bridge, the anniversary, the step and the part-time schedule, the row reads that person. Where it touches everyone, the four posted periods and the time off deducted, the row reads one employee no other rule moves, Sora Jackson for the periods and Michael Labeson for the usage. A run that applied the rule to that one applied it as a rule, and the gate catches the rest.</t>
         </is>
       </c>
       <c r="C25" s="2" t="n"/>

--- a/tasks/HR_Troutly_T2_pto_liability_close/03_show_your_work.xlsx
+++ b/tasks/HR_Troutly_T2_pto_liability_close/03_show_your_work.xlsx
@@ -1159,7 +1159,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Each witness row grades one rule on the employees that rule alone moves, so one wrong cell fails a rule once and never twice. Where the rule touches many, the row reads a group, the five capped or the five loaded tiers. Where the world applies it to one person, the bridge, the anniversary, the step and the part-time schedule, the row reads that person. Where it touches everyone, the four posted periods and the time off deducted, the row reads one employee no other rule moves, Sora Jackson for the periods and Michael Labeson for the usage. A run that applied the rule to that one applied it as a rule, and the gate catches the rest.</t>
+          <t>Each witness row tests one rule. It reads only the employees whose numbers change when that rule is missed and nothing else is. That is why one wrong cell fails a rule once and never twice. Some rules touch several people, so the row reads several. The cap reads five capped employees and the tiers read five migrated records. Some rules touch one person in this world. The bridge, the anniversary, the step and the part-time schedule each read that one person. Two rules touch everyone, the four pay periods and the time off taken. For those the row reads one person, Sora Jackson for the periods and Michael Labeson for the time off. If a run got the rule right for that one person, it got the rule right. The gate checks the other 51 through the total.</t>
         </is>
       </c>
       <c r="C25" s="2" t="n"/>

--- a/tasks/HR_Troutly_T2_pto_liability_close/03_show_your_work.xlsx
+++ b/tasks/HR_Troutly_T2_pto_liability_close/03_show_your_work.xlsx
@@ -1159,7 +1159,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Each witness row tests one rule. It reads only the employees whose numbers change when that rule is missed and nothing else is. That is why one wrong cell fails a rule once and never twice. Some rules touch several people, so the row reads several. The cap reads five capped employees and the tiers read five migrated records. Some rules touch one person in this world. The bridge, the anniversary, the step and the part-time schedule each read that one person. Two rules touch everyone, the four pay periods and the time off taken. For those the row reads one person, Sora Jackson for the periods and Michael Labeson for the time off. If a run got the rule right for that one person, it got the rule right. The gate checks the other 51 through the total.</t>
+          <t>Rows 6 to 18 each test one rule. Each reads only the employees whose numbers change when that rule is missed and nothing else is. That is why one wrong cell fails a rule once and never twice. Some rules touch several people, so the row reads several. The cap reads five capped employees and the tiers read five migrated records. Some rules touch one person in this world. The bridge, the anniversary, the step and the part-time schedule each read that one person. Two rules touch everyone, the four pay periods and the time off taken. For those the row reads one person, Sora Jackson for the periods and Michael Labeson for the time off. If a run got the rule right for that one person, it got the rule right. The gate checks the other 51 through the total.</t>
         </is>
       </c>
       <c r="C25" s="2" t="n"/>

--- a/tasks/HR_Troutly_T2_pto_liability_close/03_show_your_work.xlsx
+++ b/tasks/HR_Troutly_T2_pto_liability_close/03_show_your_work.xlsx
@@ -1159,7 +1159,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Rows 6 to 18 each test one rule. Each reads only the employees whose numbers change when that rule is missed and nothing else is. That is why one wrong cell fails a rule once and never twice. Some rules touch several people, so the row reads several. The cap reads five capped employees and the tiers read five migrated records. Some rules touch one person in this world. The bridge, the anniversary, the step and the part-time schedule each read that one person. Two rules touch everyone, the four pay periods and the time off taken. For those the row reads one person, Sora Jackson for the periods and Michael Labeson for the time off. If a run got the rule right for that one person, it got the rule right. The gate checks the other 51 through the total.</t>
+          <t>Rows 6 to 18 each test one rule on the people that rule alone moves, a group where it touches many and one person where it touches one. One wrong cell fails a rule once and never twice. Where a rule touches everyone, the periods and the time off, one clean case stands for all and the gate checks the rest.</t>
         </is>
       </c>
       <c r="C25" s="2" t="n"/>

--- a/tasks/HR_Troutly_T2_pto_liability_close/03_show_your_work.xlsx
+++ b/tasks/HR_Troutly_T2_pto_liability_close/03_show_your_work.xlsx
@@ -1159,7 +1159,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Rows 6 to 18 each test one rule on the people that rule alone moves, a group where it touches many and one person where it touches one. One wrong cell fails a rule once and never twice. Where a rule touches everyone, the periods and the time off, one clean case stands for all and the gate checks the rest.</t>
+          <t>Rows 6 to 18 each test one rule on the people that rule alone moves. One wrong cell fails a rule once and never twice. Where a rule touches everyone, one clean case stands for all and the gate checks the rest.</t>
         </is>
       </c>
       <c r="C25" s="2" t="n"/>

--- a/tasks/HR_Troutly_T2_pto_liability_close/03_show_your_work.xlsx
+++ b/tasks/HR_Troutly_T2_pto_liability_close/03_show_your_work.xlsx
@@ -1159,7 +1159,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Rows 6 to 18 each test one rule on the people that rule alone moves. One wrong cell fails a rule once and never twice. Where a rule touches everyone, one clean case stands for all and the gate checks the rest.</t>
+          <t>Rows 6 to 18 each test one rule on the people that rule alone moves. One wrong cell fails a rule once and never twice. Two rules apply to all 52 people, the four pay periods and the time off taken. Each is tested on one person whose number no other rule changes, and the total checks everyone else.</t>
         </is>
       </c>
       <c r="C25" s="2" t="n"/>

--- a/tasks/HR_Troutly_T2_pto_liability_close/03_show_your_work.xlsx
+++ b/tasks/HR_Troutly_T2_pto_liability_close/03_show_your_work.xlsx
@@ -1159,7 +1159,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Rows 6 to 18 each test one rule on the people that rule alone moves. One wrong cell fails a rule once and never twice. Two rules apply to all 52 people, the four pay periods and the time off taken. Each is tested on one person whose number no other rule changes, and the total checks everyone else.</t>
+          <t>Rows 6 to 18 each test one rule on the people that rule alone moves. One wrong cell fails a rule once and never twice.</t>
         </is>
       </c>
       <c r="C25" s="2" t="n"/>

--- a/tasks/HR_Troutly_T2_pto_liability_close/03_show_your_work.xlsx
+++ b/tasks/HR_Troutly_T2_pto_liability_close/03_show_your_work.xlsx
@@ -1173,7 +1173,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Rows 2, 14, 15 and 16 grade the population on the set of IDs. Rows 19 to 21 grade BambooHR on its tables.</t>
+          <t>Rows 14, 15 and 16 each test one place the world breaks the definition of a current employee, the contractors, the ended and the two unloaded hires. Row 2 tests the set as a whole. Rows 19 to 21 test BambooHR the same way, the six policies, the 52 balances and the two rows created, each once.</t>
         </is>
       </c>
       <c r="C26" s="2" t="n"/>

--- a/tasks/HR_Troutly_T2_pto_liability_close/03_show_your_work.xlsx
+++ b/tasks/HR_Troutly_T2_pto_liability_close/03_show_your_work.xlsx
@@ -722,7 +722,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -831,15 +831,15 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>States, on the PTO liability page, a total dollar liability of $92,739.54.</t>
+          <t>States, on the PTO liability page, a name and a department on every employee row.</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Critical value</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -849,11 +849,11 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>States, on the PTO liability page, balances of 64.62, 64.62, 58.46, 58.46 and 58.46 hours for TRT-0005, TRT-0009, TRT-0014, TRT-0023 and TRT-0040, the five above 40.0 hours at 06/30/2026 whose balance the cap alone moves.</t>
+          <t>States, on the PTO liability page, the summary above one table of employee rows.</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -867,15 +867,15 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>States, on the PTO liability page, the 120-hour tier for TRT-0043, TRT-0051, TRT-0058, TRT-0079 and TRT-0083.</t>
+          <t>States, on the PTO liability page, a total dollar liability of $92,739.54.</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Critical value</t>
         </is>
       </c>
     </row>
@@ -885,11 +885,11 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>States, on the PTO liability page, the 160-hour tier for Samuel Burkenham, TRT-0071, with service bridged to 03/08/2021.</t>
+          <t>States, on the PTO liability page, a balance of 64.62 hours for Mikelle Hosana, TRT-0005.</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -903,11 +903,11 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>States, on the PTO liability page, an accrual of 20.0000 hours for Marisela Thornbury, TRT-0018, three periods at the 120-hour tier and one at 160.</t>
+          <t>States, on the PTO liability page, the 120-hour tier for Oren Kastellanos, TRT-0043.</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
@@ -921,7 +921,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>States, on the PTO liability page, an hourly rate of $56.7308 for Yolanda Featherstone, TRT-0088.</t>
+          <t>States, on the PTO liability page, the 160-hour tier for Samuel Burkenham, TRT-0071.</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
@@ -939,7 +939,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>States, on the PTO liability page, an hourly rate of $71.2500 for Belaviv Luk, TRT-0117.</t>
+          <t>States, on the PTO liability page, a balance of 60.00 hours for Marisela Thornbury, TRT-0018.</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
@@ -957,11 +957,11 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>States, on the PTO liability page, an hourly rate of $29.3269 for Delphine Marchetti, TRT-0096.</t>
+          <t>States, on the PTO liability page, an hourly rate of $56.7308 for Yolanda Featherstone, TRT-0088.</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
@@ -975,11 +975,11 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>States, on the PTO liability page, a balance of 29.60 hours for Beatriz Quintanilla, TRT-0141.</t>
+          <t>States, on the PTO liability page, an hourly rate of $71.2500 for Belaviv Luk, TRT-0117.</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
@@ -993,11 +993,11 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>States, on the PTO liability page, no contractor row, CTR-2001 to CTR-2004.</t>
+          <t>States, on the PTO liability page, an hourly rate of $29.3269 for Delphine Marchetti, TRT-0096.</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>States, on the PTO liability page, no row for TRT-0037, TRT-0049, TRT-0064 or TRT-0006.</t>
+          <t>States, on the PTO liability page, a balance of 29.60 hours for Beatriz Quintanilla, TRT-0141.</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>States, on the PTO liability page, Simone Okonkwo, TRT-0153, and Rafael Ibarra, TRT-0155, at the 80-hour tier with accruals since their start dates.</t>
+          <t>States, on the PTO liability page, no contractor row, CTR-2001 to CTR-2004.</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
@@ -1047,11 +1047,11 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>States, on the PTO liability page, a balance of 62.62 hours for Sora Jackson, TRT-0002, four posted periods at the 160-hour tier.</t>
+          <t>States, on the PTO liability page, no row for Piper Athanasoulis, TRT-0037.</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
@@ -1065,11 +1065,11 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>States, on the PTO liability page, a balance of 22.87 hours for Michael Labeson, TRT-0001, with 40.00 hours of approved time off deducted.</t>
+          <t>States, on the PTO liability page, no row for Halston Perevalov, TRT-0049.</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
@@ -1083,11 +1083,11 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>States, in BambooHR, the PTO policy the schedule's tier gives for each of the 6 employees whose loaded policy differed.</t>
+          <t>States, on the PTO liability page, no row for Marguerite Delacroix-Hahn, TRT-0064.</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
@@ -1101,11 +1101,11 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>States, in BambooHR, a PTO balance equal to the schedule's 08/31/2026 balance for every employee on the schedule.</t>
+          <t>States, on the PTO liability page, no row for Grayson Oshimoto, TRT-0006.</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
@@ -1119,7 +1119,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>States, in BambooHR, a PTO balance row for TRT-0153 and TRT-0155.</t>
+          <t>States, on the PTO liability page, a balance of 6.15 hours for Simone Okonkwo, TRT-0153.</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
@@ -1132,52 +1132,178 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="n"/>
-      <c r="B23" s="2" t="n"/>
-      <c r="C23" s="2" t="n"/>
-      <c r="D23" s="2" t="n"/>
+      <c r="A23" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>States, on the PTO liability page, a balance of 3.08 hours for Rafael Ibarra, TRT-0155.</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+      <c r="A24" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>States, on the PTO liability page, a balance of 62.62 hours for Sora Jackson, TRT-0002.</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>States, on the PTO liability page, a balance of 22.87 hours for Michael Labeson, TRT-0001.</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>States, in BambooHR, a PTO policy matching the schedule's tier for each of the 50 employees on the schedule other than TRT-0153 and TRT-0155.</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>States, in BambooHR, a PTO balance equal to the schedule's 08/31/2026 balance for each of the 50 employees on the schedule other than TRT-0153 and TRT-0155.</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>States, in BambooHR, a PTO balance of 6.15 hours for Simone Okonkwo, TRT-0153.</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>States, in BambooHR, a PTO balance of 3.08 hours for Rafael Ibarra, TRT-0155.</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="n"/>
+      <c r="B30" s="2" t="n"/>
+      <c r="C30" s="2" t="n"/>
+      <c r="D30" s="2" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>The gate grades every rule across the whole group at once. It reads the total of all 52 liabilities, the one number all 364 cells feed, and it matches the schedule's only if every entry is right.</t>
         </is>
       </c>
-      <c r="C24" s="2" t="n"/>
-      <c r="D24" s="2" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+      <c r="C31" s="2" t="n"/>
+      <c r="D31" s="2" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>Rows 6 to 18 each test one rule on the people that rule alone moves. One wrong cell fails a rule once and never twice.</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="n"/>
-      <c r="D25" s="2" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Rows 8 to 15, 23 and 24 each test one rule on one employee that rule alone moves. One wrong cell fails a rule once and never twice.</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="n"/>
+      <c r="D32" s="2" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>Rows 14, 15 and 16 each test one place the world breaks the definition of a current employee, the contractors, the ended and the two unloaded hires. Row 2 tests the set as a whole. Rows 19 to 21 test BambooHR the same way, the six policies, the 52 balances and the two rows created, each once.</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="n"/>
-      <c r="D26" s="2" t="n"/>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>Rows 16 to 22 each test one place the world breaks the definition of a current employee, the contractors, the four ended and the two unloaded hires. Row 2 tests the set as a whole. Rows 25 to 28 test BambooHR, the 50 loaded policies and balances as two sets and the two rows created, each once.</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="n"/>
+      <c r="D33" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/tasks/HR_Troutly_T2_pto_liability_close/03_show_your_work.xlsx
+++ b/tasks/HR_Troutly_T2_pto_liability_close/03_show_your_work.xlsx
@@ -722,7 +722,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D33"/>
+  <dimension ref="A1:D49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -795,7 +795,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>States, on the PTO liability page, hours to two decimals, hourly rates to four decimals, dollars to the cent and a total equal to the sum of the rows.</t>
+          <t>States, on the PTO liability page, hours to two decimals, hourly rates to four decimals and dollars to the cent.</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
@@ -813,7 +813,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>States, on the PTO liability page, a summary with the employee count, the total hours and the total dollar liability.</t>
+          <t>States, on the PTO liability page, a total dollar liability equal to the sum of the rows.</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
@@ -831,7 +831,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>States, on the PTO liability page, a name and a department on every employee row.</t>
+          <t>States, on the PTO liability page, a summary with the employee count, the total hours and the total dollar liability.</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
@@ -849,7 +849,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>States, on the PTO liability page, the summary above one table of employee rows.</t>
+          <t>States, on the PTO liability page, a name, a department and an annual PTO tier on every employee row.</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
@@ -867,15 +867,15 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>States, on the PTO liability page, a total dollar liability of $92,739.54.</t>
+          <t>States, on the PTO liability page, an employee ID on every row.</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Critical value</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -885,11 +885,11 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>States, on the PTO liability page, a balance of 64.62 hours for Mikelle Hosana, TRT-0005.</t>
+          <t>States, on the PTO liability page, every date in MM/DD/YYYY form.</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -903,11 +903,11 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>States, on the PTO liability page, the 120-hour tier for Oren Kastellanos, TRT-0043.</t>
+          <t>States, on the PTO liability page, the summary above one table of employee rows.</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
@@ -921,15 +921,15 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>States, on the PTO liability page, the 160-hour tier for Samuel Burkenham, TRT-0071.</t>
+          <t>States, on the PTO liability page, a total dollar liability of $92,739.54.</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Critical value</t>
         </is>
       </c>
     </row>
@@ -939,11 +939,11 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>States, on the PTO liability page, a balance of 60.00 hours for Marisela Thornbury, TRT-0018.</t>
+          <t>States, on the PTO liability page, a balance of 64.62 hours for Mikelle Hosana, TRT-0005.</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
@@ -957,11 +957,11 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>States, on the PTO liability page, an hourly rate of $56.7308 for Yolanda Featherstone, TRT-0088.</t>
+          <t>States, on the PTO liability page, the 120-hour tier for Oren Kastellanos, TRT-0043.</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
@@ -975,11 +975,11 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>States, on the PTO liability page, an hourly rate of $71.2500 for Belaviv Luk, TRT-0117.</t>
+          <t>States, on the PTO liability page, the 160-hour tier for Samuel Burkenham, TRT-0071.</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
@@ -993,11 +993,11 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>States, on the PTO liability page, an hourly rate of $29.3269 for Delphine Marchetti, TRT-0096.</t>
+          <t>States, on the PTO liability page, a balance of 60.00 hours for Marisela Thornbury, TRT-0018.</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
@@ -1011,11 +1011,11 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>States, on the PTO liability page, a balance of 29.60 hours for Beatriz Quintanilla, TRT-0141.</t>
+          <t>States, on the PTO liability page, an hourly rate of $56.7308 for Yolanda Featherstone, TRT-0088.</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
@@ -1029,11 +1029,11 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>States, on the PTO liability page, no contractor row, CTR-2001 to CTR-2004.</t>
+          <t>States, on the PTO liability page, an hourly rate of $71.2500 for Belaviv Luk, TRT-0117.</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
@@ -1047,11 +1047,11 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>States, on the PTO liability page, no row for Piper Athanasoulis, TRT-0037.</t>
+          <t>States, on the PTO liability page, an hourly rate of $29.3269 for Delphine Marchetti, TRT-0096.</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
@@ -1065,11 +1065,11 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>States, on the PTO liability page, no row for Halston Perevalov, TRT-0049.</t>
+          <t>States, on the PTO liability page, a balance of 29.60 hours for Beatriz Quintanilla, TRT-0141.</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
@@ -1083,11 +1083,11 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>States, on the PTO liability page, no row for Marguerite Delacroix-Hahn, TRT-0064.</t>
+          <t>States, on the PTO liability page, no contractor row, CTR-2001 to CTR-2004.</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>States, on the PTO liability page, no row for Grayson Oshimoto, TRT-0006.</t>
+          <t>States, on the PTO liability page, no row for Piper Athanasoulis, TRT-0037.</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
@@ -1119,11 +1119,11 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>States, on the PTO liability page, a balance of 6.15 hours for Simone Okonkwo, TRT-0153.</t>
+          <t>States, on the PTO liability page, no row for Halston Perevalov, TRT-0049.</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
@@ -1137,11 +1137,11 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>States, on the PTO liability page, a balance of 3.08 hours for Rafael Ibarra, TRT-0155.</t>
+          <t>States, on the PTO liability page, no row for Marguerite Delacroix-Hahn, TRT-0064.</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
@@ -1155,11 +1155,11 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>States, on the PTO liability page, a balance of 62.62 hours for Sora Jackson, TRT-0002.</t>
+          <t>States, on the PTO liability page, no row for Grayson Oshimoto, TRT-0006.</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>States, on the PTO liability page, a balance of 22.87 hours for Michael Labeson, TRT-0001.</t>
+          <t>States, on the PTO liability page, a balance of 6.15 hours for Simone Okonkwo, TRT-0153.</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
@@ -1191,11 +1191,11 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>States, in BambooHR, a PTO policy matching the schedule's tier for each of the 50 employees on the schedule other than TRT-0153 and TRT-0155.</t>
+          <t>States, on the PTO liability page, a balance of 3.08 hours for Rafael Ibarra, TRT-0155.</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
@@ -1209,11 +1209,11 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>States, in BambooHR, a PTO balance equal to the schedule's 08/31/2026 balance for each of the 50 employees on the schedule other than TRT-0153 and TRT-0155.</t>
+          <t>States, on the PTO liability page, a balance of 62.62 hours for Sora Jackson, TRT-0002.</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
@@ -1227,11 +1227,11 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>States, in BambooHR, a PTO balance of 6.15 hours for Simone Okonkwo, TRT-0153.</t>
+          <t>States, on the PTO liability page, a balance of 22.87 hours for Michael Labeson, TRT-0001.</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
@@ -1245,7 +1245,7 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>States, in BambooHR, a PTO balance of 3.08 hours for Rafael Ibarra, TRT-0155.</t>
+          <t>States, in BambooHR, the PTO 2 to 5 Years policy for Oren Kastellanos, TRT-0043.</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
@@ -1258,52 +1258,336 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="n"/>
-      <c r="B30" s="2" t="n"/>
-      <c r="C30" s="2" t="n"/>
-      <c r="D30" s="2" t="n"/>
+      <c r="A30" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>States, in BambooHR, the PTO 2 to 5 Years policy for Priyamvada Raghunath, TRT-0051.</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+      <c r="A31" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>States, in BambooHR, the PTO 2 to 5 Years policy for Callum Oyelaran, TRT-0058.</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>States, in BambooHR, the PTO 5 Plus Years policy for Samuel Burkenham, TRT-0071.</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>States, in BambooHR, the PTO 2 to 5 Years policy for Wren Takahashi-Bell, TRT-0079.</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>States, in BambooHR, the PTO 2 to 5 Years policy for Desmond Achterberg, TRT-0083.</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>States, in BambooHR, no PTO policy change on the 44 employees whose loaded policy is the schedule's tier.</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>States, in BambooHR, a PTO balance of 64.62 hours for Mikelle Hosana, TRT-0005.</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>States, in BambooHR, a PTO balance of 34.46 hours for Oren Kastellanos, TRT-0043.</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>States, in BambooHR, a PTO balance of 51.87 hours for Samuel Burkenham, TRT-0071.</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>States, in BambooHR, a PTO balance of 60.00 hours for Marisela Thornbury, TRT-0018.</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>States, in BambooHR, a PTO balance of 29.60 hours for Beatriz Quintanilla, TRT-0141.</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>States, in BambooHR, no PTO balance change on the 33 employees whose loaded balance is the schedule's.</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>States, in BambooHR, a PTO balance of 6.15 hours for Simone Okonkwo, TRT-0153.</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>States, in BambooHR, a PTO balance of 3.08 hours for Rafael Ibarra, TRT-0155.</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>States, in Greenhouse, every table as seeded, with no row added, changed or removed.</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="n"/>
+      <c r="B45" s="2" t="n"/>
+      <c r="C45" s="2" t="n"/>
+      <c r="D45" s="2" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>The gate grades every rule across the whole group at once. It reads the total of all 52 liabilities, the one number all 364 cells feed, and it matches the schedule's only if every entry is right.</t>
         </is>
       </c>
-      <c r="C31" s="2" t="n"/>
-      <c r="D31" s="2" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+      <c r="C46" s="2" t="n"/>
+      <c r="D46" s="2" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>Rows 8 to 15, 23 and 24 each test one rule on one employee that rule alone moves. One wrong cell fails a rule once and never twice.</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="n"/>
-      <c r="D32" s="2" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>Rows 11 to 18 and 24 to 27 each test one rule on one employee that rule alone moves. One wrong cell fails a rule once and never twice.</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="n"/>
+      <c r="D47" s="2" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>Rows 16 to 22 each test one place the world breaks the definition of a current employee, the contractors, the four ended and the two unloaded hires. Row 2 tests the set as a whole. Rows 25 to 28 test BambooHR, the 50 loaded policies and balances as two sets and the two rows created, each once.</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="n"/>
-      <c r="D33" s="2" t="n"/>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>Rows 19 to 23 each test one place the world breaks the definition of a current employee, the contractors and the four ended, and rows 24 to 25 the two unloaded hires. Row 2 tests the set as a whole.</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="n"/>
+      <c r="D48" s="2" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>Rows 28 to 42 test BambooHR. One policy for each of the six records the schedule moves, one balance for each of five rules mirrored there, the two rows created, and two guards over the 44 policies and 33 balances the schedule leaves as loaded. Row 43 tests Greenhouse untouched.</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="n"/>
+      <c r="D49" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1451,7 +1735,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Six policies reassigned, 52 balances set, rows created for TRT-0153 and TRT-0155.</t>
+          <t>Six policies reassigned and 44 left as loaded. 17 balances moved and 33 left as loaded. Rows created for TRT-0153 and TRT-0155. Greenhouse untouched.</t>
         </is>
       </c>
     </row>

--- a/tasks/HR_Troutly_T2_pto_liability_close/03_show_your_work.xlsx
+++ b/tasks/HR_Troutly_T2_pto_liability_close/03_show_your_work.xlsx
@@ -722,7 +722,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D49"/>
+  <dimension ref="A1:D50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>States, in BambooHR, no PTO policy change on the 44 employees whose loaded policy is the schedule's tier.</t>
+          <t>States, in BambooHR, the schedule's PTO policy for each of the 44 employees whose loaded policy is the schedule's tier.</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
@@ -1461,7 +1461,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>States, in BambooHR, no PTO balance change on the 33 employees whose loaded balance is the schedule's.</t>
+          <t>States, in BambooHR, the schedule's PTO balance for each of the 33 employees whose loaded balance is the schedule's.</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
@@ -1515,7 +1515,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>States, in Greenhouse, every table as seeded, with no row added, changed or removed.</t>
+          <t>States, in BambooHR, the PTO Under 2 Years policy for Simone Okonkwo, TRT-0153.</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
@@ -1528,22 +1528,26 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="n"/>
-      <c r="B45" s="2" t="n"/>
-      <c r="C45" s="2" t="n"/>
-      <c r="D45" s="2" t="n"/>
+      <c r="A45" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>States, in BambooHR, the PTO Under 2 Years policy for Rafael Ibarra, TRT-0155.</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>Note</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>The gate grades every rule across the whole group at once. It reads the total of all 52 liabilities, the one number all 364 cells feed, and it matches the schedule's only if every entry is right.</t>
-        </is>
-      </c>
+      <c r="A46" s="2" t="n"/>
+      <c r="B46" s="2" t="n"/>
       <c r="C46" s="2" t="n"/>
       <c r="D46" s="2" t="n"/>
     </row>
@@ -1555,7 +1559,7 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Rows 11 to 18 and 24 to 27 each test one rule on one employee that rule alone moves. One wrong cell fails a rule once and never twice.</t>
+          <t>The gate grades every rule across the whole group at once. It reads the total of all 52 liabilities, the one number all 364 cells feed, and it matches the schedule's only if every entry is right.</t>
         </is>
       </c>
       <c r="C47" s="2" t="n"/>
@@ -1569,7 +1573,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Rows 19 to 23 each test one place the world breaks the definition of a current employee, the contractors and the four ended, and rows 24 to 25 the two unloaded hires. Row 2 tests the set as a whole.</t>
+          <t>Rows 11 to 18 and 24 to 27 each test one rule on one employee that rule alone moves. One wrong cell fails a rule once and never twice.</t>
         </is>
       </c>
       <c r="C48" s="2" t="n"/>
@@ -1583,11 +1587,25 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>Rows 28 to 42 test BambooHR. One policy for each of the six records the schedule moves, one balance for each of five rules mirrored there, the two rows created, and two guards over the 44 policies and 33 balances the schedule leaves as loaded. Row 43 tests Greenhouse untouched.</t>
+          <t>Rows 19 to 23 each test one place the world breaks the definition of a current employee, the contractors and the four ended, and rows 24 to 25 the two unloaded hires. Row 2 tests the set as a whole.</t>
         </is>
       </c>
       <c r="C49" s="2" t="n"/>
       <c r="D49" s="2" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>Rows 28 to 44 test BambooHR. One policy for each of the six records the schedule moves, one balance for each of five rules mirrored there, a balance and a policy for each of the two records created, and two rows over the 44 policies and 33 balances the schedule leaves as loaded.</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="n"/>
+      <c r="D50" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1735,7 +1753,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Six policies reassigned and 44 left as loaded. 17 balances moved and 33 left as loaded. Rows created for TRT-0153 and TRT-0155. Greenhouse untouched.</t>
+          <t>Six policies reassigned and 44 left as loaded. 17 balances moved and 33 left as loaded. Rows created for TRT-0153 and TRT-0155 with the 80-hour policy.</t>
         </is>
       </c>
     </row>

--- a/tasks/HR_Troutly_T2_pto_liability_close/03_show_your_work.xlsx
+++ b/tasks/HR_Troutly_T2_pto_liability_close/03_show_your_work.xlsx
@@ -722,7 +722,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D50"/>
+  <dimension ref="A1:D54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -777,7 +777,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>States, on the PTO liability page, the 52 current employees at 08/31/2026 as the only employee rows.</t>
+          <t>States, on the PTO liability page, an employee row for each of the 52 current employees at 08/31/2026.</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
@@ -795,7 +795,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>States, on the PTO liability page, hours to two decimals, hourly rates to four decimals and dollars to the cent.</t>
+          <t>States, on the PTO liability page, hours to two decimals.</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
@@ -813,7 +813,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>States, on the PTO liability page, a total dollar liability equal to the sum of the rows.</t>
+          <t>States, on the PTO liability page, hourly rates to four decimals.</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
@@ -831,7 +831,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>States, on the PTO liability page, a summary with the employee count, the total hours and the total dollar liability.</t>
+          <t>States, on the PTO liability page, dollars to the cent.</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
@@ -849,7 +849,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>States, on the PTO liability page, a name, a department and an annual PTO tier on every employee row.</t>
+          <t>States, on the PTO liability page, a total dollar liability equal to the sum of the rows.</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
@@ -867,7 +867,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>States, on the PTO liability page, an employee ID on every row.</t>
+          <t>States, on the PTO liability page, a summary with the employee count, the total hours and the total dollar liability.</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
@@ -885,7 +885,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>States, on the PTO liability page, every date in MM/DD/YYYY form.</t>
+          <t>States, on the PTO liability page, a name on every employee row.</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
@@ -903,7 +903,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>States, on the PTO liability page, the summary above one table of employee rows.</t>
+          <t>States, on the PTO liability page, a department on every employee row.</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
@@ -921,15 +921,15 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>States, on the PTO liability page, a total dollar liability of $92,739.54.</t>
+          <t>States, on the PTO liability page, an annual PTO tier in hours on every employee row.</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Critical value</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -939,11 +939,11 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>States, on the PTO liability page, a balance of 64.62 hours for Mikelle Hosana, TRT-0005.</t>
+          <t>States, on the PTO liability page, an employee ID on every row.</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
@@ -957,11 +957,11 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>States, on the PTO liability page, the 120-hour tier for Oren Kastellanos, TRT-0043.</t>
+          <t>States, on the PTO liability page, every date in MM/DD/YYYY form.</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
@@ -975,11 +975,11 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>States, on the PTO liability page, the 160-hour tier for Samuel Burkenham, TRT-0071.</t>
+          <t>States, on the PTO liability page, the summary above one table of employee rows.</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
@@ -993,15 +993,15 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>States, on the PTO liability page, a balance of 60.00 hours for Marisela Thornbury, TRT-0018.</t>
+          <t>States, on the PTO liability page, a total dollar liability of $92,739.54.</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Critical value</t>
         </is>
       </c>
     </row>
@@ -1011,11 +1011,11 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>States, on the PTO liability page, an hourly rate of $56.7308 for Yolanda Featherstone, TRT-0088.</t>
+          <t>States, on the PTO liability page, a balance of 64.62 hours for Mikelle Hosana, TRT-0005.</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
@@ -1029,11 +1029,11 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>States, on the PTO liability page, an hourly rate of $71.2500 for Belaviv Luk, TRT-0117.</t>
+          <t>States, on the PTO liability page, the 120-hour tier for Oren Kastellanos, TRT-0043.</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
@@ -1047,11 +1047,11 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>States, on the PTO liability page, an hourly rate of $29.3269 for Delphine Marchetti, TRT-0096.</t>
+          <t>States, on the PTO liability page, the 160-hour tier for Samuel Burkenham, TRT-0071.</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
@@ -1065,11 +1065,11 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>States, on the PTO liability page, a balance of 29.60 hours for Beatriz Quintanilla, TRT-0141.</t>
+          <t>States, on the PTO liability page, a balance of 60.00 hours for Marisela Thornbury, TRT-0018.</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
@@ -1083,11 +1083,11 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>States, on the PTO liability page, no contractor row, CTR-2001 to CTR-2004.</t>
+          <t>States, on the PTO liability page, an hourly rate of $56.7308 for Yolanda Featherstone, TRT-0088.</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
@@ -1101,11 +1101,11 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>States, on the PTO liability page, no row for Piper Athanasoulis, TRT-0037.</t>
+          <t>States, on the PTO liability page, an hourly rate of $71.2500 for Belaviv Luk, TRT-0117.</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
@@ -1119,11 +1119,11 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>States, on the PTO liability page, no row for Halston Perevalov, TRT-0049.</t>
+          <t>States, on the PTO liability page, an hourly rate of $29.3269 for Delphine Marchetti, TRT-0096.</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
@@ -1137,11 +1137,11 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>States, on the PTO liability page, no row for Marguerite Delacroix-Hahn, TRT-0064.</t>
+          <t>States, on the PTO liability page, a balance of 29.60 hours for Beatriz Quintanilla, TRT-0141.</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
@@ -1155,11 +1155,11 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>States, on the PTO liability page, no row for Grayson Oshimoto, TRT-0006.</t>
+          <t>States, on the PTO liability page, no contractor row, CTR-2001 to CTR-2004.</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
@@ -1173,11 +1173,11 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>States, on the PTO liability page, a balance of 6.15 hours for Simone Okonkwo, TRT-0153.</t>
+          <t>States, on the PTO liability page, no row for Piper Athanasoulis, TRT-0037.</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
@@ -1191,11 +1191,11 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>States, on the PTO liability page, a balance of 3.08 hours for Rafael Ibarra, TRT-0155.</t>
+          <t>States, on the PTO liability page, no row for Halston Perevalov, TRT-0049.</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
@@ -1209,11 +1209,11 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>States, on the PTO liability page, a balance of 62.62 hours for Sora Jackson, TRT-0002.</t>
+          <t>States, on the PTO liability page, no row for Marguerite Delacroix-Hahn, TRT-0064.</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
@@ -1227,11 +1227,11 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>States, on the PTO liability page, a balance of 22.87 hours for Michael Labeson, TRT-0001.</t>
+          <t>States, on the PTO liability page, no row for Grayson Oshimoto, TRT-0006.</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
@@ -1245,11 +1245,11 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>States, in BambooHR, the PTO 2 to 5 Years policy for Oren Kastellanos, TRT-0043.</t>
+          <t>States, on the PTO liability page, a balance of 6.15 hours for Simone Okonkwo, TRT-0153.</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
@@ -1263,11 +1263,11 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>States, in BambooHR, the PTO 2 to 5 Years policy for Priyamvada Raghunath, TRT-0051.</t>
+          <t>States, on the PTO liability page, a balance of 3.08 hours for Rafael Ibarra, TRT-0155.</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
@@ -1281,11 +1281,11 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>States, in BambooHR, the PTO 2 to 5 Years policy for Callum Oyelaran, TRT-0058.</t>
+          <t>States, on the PTO liability page, a balance of 62.62 hours for Sora Jackson, TRT-0002.</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
@@ -1299,11 +1299,11 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>States, in BambooHR, the PTO 5 Plus Years policy for Samuel Burkenham, TRT-0071.</t>
+          <t>States, on the PTO liability page, a balance of 22.87 hours for Michael Labeson, TRT-0001.</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
@@ -1317,7 +1317,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>States, in BambooHR, the PTO 2 to 5 Years policy for Wren Takahashi-Bell, TRT-0079.</t>
+          <t>States, in BambooHR, the PTO 2 to 5 Years policy for Oren Kastellanos, TRT-0043.</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
@@ -1335,7 +1335,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>States, in BambooHR, the PTO 2 to 5 Years policy for Desmond Achterberg, TRT-0083.</t>
+          <t>States, in BambooHR, the PTO 2 to 5 Years policy for Priyamvada Raghunath, TRT-0051.</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
@@ -1353,7 +1353,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>States, in BambooHR, the schedule's PTO policy for each of the 44 employees whose loaded policy is the schedule's tier.</t>
+          <t>States, in BambooHR, the PTO 2 to 5 Years policy for Callum Oyelaran, TRT-0058.</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>States, in BambooHR, a PTO balance of 64.62 hours for Mikelle Hosana, TRT-0005.</t>
+          <t>States, in BambooHR, the PTO 5 Plus Years policy for Samuel Burkenham, TRT-0071.</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>States, in BambooHR, a PTO balance of 34.46 hours for Oren Kastellanos, TRT-0043.</t>
+          <t>States, in BambooHR, the PTO 2 to 5 Years policy for Wren Takahashi-Bell, TRT-0079.</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>States, in BambooHR, a PTO balance of 51.87 hours for Samuel Burkenham, TRT-0071.</t>
+          <t>States, in BambooHR, the PTO 2 to 5 Years policy for Desmond Achterberg, TRT-0083.</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
@@ -1425,7 +1425,7 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>States, in BambooHR, a PTO balance of 60.00 hours for Marisela Thornbury, TRT-0018.</t>
+          <t>States, in BambooHR, for the 44 employees whose loaded policy is the tier's at 08/31/2026, the PTO Under 2 Years policy for TRT-0096, TRT-0099, TRT-0102, TRT-0105, TRT-0108, TRT-0110, TRT-0113, TRT-0119, TRT-0122, TRT-0128, TRT-0131, TRT-0135, TRT-0141, TRT-0150, TRT-0154, TRT-0156, the PTO 2 to 5 Years policy for TRT-0012, TRT-0014, TRT-0021, TRT-0023, TRT-0027, TRT-0029, TRT-0031, TRT-0034, TRT-0040, TRT-0045, TRT-0047, TRT-0052, TRT-0055, TRT-0062, TRT-0066, TRT-0069, TRT-0074, TRT-0076, TRT-0086, TRT-0088, TRT-0091, TRT-0093, TRT-0117, the PTO 5 Plus Years policy for TRT-0001, TRT-0002, TRT-0005, TRT-0009, TRT-0018.</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
@@ -1443,7 +1443,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>States, in BambooHR, a PTO balance of 29.60 hours for Beatriz Quintanilla, TRT-0141.</t>
+          <t>States, in BambooHR, a PTO balance of 64.62 hours for Mikelle Hosana, TRT-0005.</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
@@ -1461,7 +1461,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>States, in BambooHR, the schedule's PTO balance for each of the 33 employees whose loaded balance is the schedule's.</t>
+          <t>States, in BambooHR, a PTO balance of 34.46 hours for Oren Kastellanos, TRT-0043.</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
@@ -1479,7 +1479,7 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>States, in BambooHR, a PTO balance of 6.15 hours for Simone Okonkwo, TRT-0153.</t>
+          <t>States, in BambooHR, a PTO balance of 51.87 hours for Samuel Burkenham, TRT-0071.</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
@@ -1497,7 +1497,7 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>States, in BambooHR, a PTO balance of 3.08 hours for Rafael Ibarra, TRT-0155.</t>
+          <t>States, in BambooHR, a PTO balance of 60.00 hours for Marisela Thornbury, TRT-0018.</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
@@ -1515,7 +1515,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>States, in BambooHR, the PTO Under 2 Years policy for Simone Okonkwo, TRT-0153.</t>
+          <t>States, in BambooHR, a PTO balance of 29.60 hours for Beatriz Quintanilla, TRT-0141.</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
@@ -1533,7 +1533,7 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>States, in BambooHR, the PTO Under 2 Years policy for Rafael Ibarra, TRT-0155.</t>
+          <t>States, in BambooHR, for the 33 employees whose loaded balance is the 08/31/2026 figure, a PTO balance of 22.87 hours for TRT-0001, 62.62 for TRT-0002, 26.71 for TRT-0027, 30.96 for TRT-0034, 7.96 for TRT-0045, 5.46 for TRT-0047, 4.46 for TRT-0052, 15.96 for TRT-0055, 21.21 for TRT-0062, 27.96 for TRT-0066, 46.21 for TRT-0069, 44.21 for TRT-0074, 35.21 for TRT-0076, 51.96 for TRT-0086, 13.21 for TRT-0088, 25.71 for TRT-0091, 20.21 for TRT-0093, 20.56 for TRT-0096, 37.06 for TRT-0099, 24.31 for TRT-0102, 15.81 for TRT-0105, 41.31 for TRT-0108, 23.81 for TRT-0110, 26.56 for TRT-0113, 8.46 for TRT-0117, 22.06 for TRT-0119, 31.31 for TRT-0122, 20.06 for TRT-0128, 4.31 for TRT-0131, 49.31 for TRT-0135, 12.31 for TRT-0150, 3.08 for TRT-0154, 0.00 for TRT-0156.</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
@@ -1546,66 +1546,138 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="n"/>
-      <c r="B46" s="2" t="n"/>
-      <c r="C46" s="2" t="n"/>
-      <c r="D46" s="2" t="n"/>
+      <c r="A46" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>States, in BambooHR, a PTO balance of 6.15 hours for Simone Okonkwo, TRT-0153.</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>Note</t>
-        </is>
+      <c r="A47" s="2" t="n">
+        <v>46</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>The gate grades every rule across the whole group at once. It reads the total of all 52 liabilities, the one number all 364 cells feed, and it matches the schedule's only if every entry is right.</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="n"/>
-      <c r="D47" s="2" t="n"/>
+          <t>States, in BambooHR, a PTO balance of 3.08 hours for Rafael Ibarra, TRT-0155.</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>Note</t>
-        </is>
+      <c r="A48" s="2" t="n">
+        <v>47</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Rows 11 to 18 and 24 to 27 each test one rule on one employee that rule alone moves. One wrong cell fails a rule once and never twice.</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="n"/>
-      <c r="D48" s="2" t="n"/>
+          <t>States, in BambooHR, the PTO Under 2 Years policy for Simone Okonkwo, TRT-0153.</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>Note</t>
-        </is>
+      <c r="A49" s="2" t="n">
+        <v>48</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>Rows 19 to 23 each test one place the world breaks the definition of a current employee, the contractors and the four ended, and rows 24 to 25 the two unloaded hires. Row 2 tests the set as a whole.</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="n"/>
-      <c r="D49" s="2" t="n"/>
+          <t>States, in BambooHR, the PTO Under 2 Years policy for Rafael Ibarra, TRT-0155.</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>Note</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>Rows 28 to 44 test BambooHR. One policy for each of the six records the schedule moves, one balance for each of five rules mirrored there, a balance and a policy for each of the two records created, and two rows over the 44 policies and 33 balances the schedule leaves as loaded.</t>
-        </is>
-      </c>
+      <c r="A50" s="2" t="n"/>
+      <c r="B50" s="2" t="n"/>
       <c r="C50" s="2" t="n"/>
       <c r="D50" s="2" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>The gate grades every rule across the whole group at once. It reads the total of all 52 liabilities, the one number all 364 cells feed, and it matches the schedule's only if every entry is right.</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="n"/>
+      <c r="D51" s="2" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>Rows 15 to 22 and 28 to 31 each test one rule on one employee that rule alone moves. One wrong cell fails a rule once and never twice.</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="n"/>
+      <c r="D52" s="2" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>Rows 23 to 27 each test one place the world breaks the definition of a current employee, the contractors and the four ended, and rows 28 to 29 the two unloaded hires. Row 2 tests the set as a whole.</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="n"/>
+      <c r="D53" s="2" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>Rows 32 to 48 test BambooHR. One policy for each of the six records the schedule moves, one balance for each of five rules mirrored there, a balance and a policy for each of the two records created, and two rows over the 44 policies and 33 balances the schedule leaves as loaded.</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="n"/>
+      <c r="D54" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/tasks/HR_Troutly_T2_pto_liability_close/03_show_your_work.xlsx
+++ b/tasks/HR_Troutly_T2_pto_liability_close/03_show_your_work.xlsx
@@ -722,7 +722,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D54"/>
+  <dimension ref="A1:D61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -777,7 +777,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>States, on the PTO liability page, an employee row for each of the 52 current employees at 08/31/2026.</t>
+          <t>States, on the PTO liability page, the 52 current employees at 08/31/2026 as the only employee rows.</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
@@ -1155,11 +1155,11 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>States, on the PTO liability page, no contractor row, CTR-2001 to CTR-2004.</t>
+          <t>States, on the PTO liability page, a balance of 6.15 hours for Simone Okonkwo, TRT-0153.</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
@@ -1173,11 +1173,11 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>States, on the PTO liability page, no row for Piper Athanasoulis, TRT-0037.</t>
+          <t>States, on the PTO liability page, a balance of 3.08 hours for Rafael Ibarra, TRT-0155.</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
@@ -1191,11 +1191,11 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>States, on the PTO liability page, no row for Halston Perevalov, TRT-0049.</t>
+          <t>States, on the PTO liability page, a balance of 62.62 hours for Sora Jackson, TRT-0002.</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
@@ -1209,11 +1209,11 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>States, on the PTO liability page, no row for Marguerite Delacroix-Hahn, TRT-0064.</t>
+          <t>States, on the PTO liability page, a balance of 22.87 hours for Michael Labeson, TRT-0001.</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>States, on the PTO liability page, no row for Grayson Oshimoto, TRT-0006.</t>
+          <t>States, in BambooHR, the PTO 2 to 5 Years policy for Oren Kastellanos, TRT-0043.</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
@@ -1245,11 +1245,11 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>States, on the PTO liability page, a balance of 6.15 hours for Simone Okonkwo, TRT-0153.</t>
+          <t>States, in BambooHR, the PTO 2 to 5 Years policy for Priyamvada Raghunath, TRT-0051.</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
@@ -1263,11 +1263,11 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>States, on the PTO liability page, a balance of 3.08 hours for Rafael Ibarra, TRT-0155.</t>
+          <t>States, in BambooHR, the PTO 2 to 5 Years policy for Callum Oyelaran, TRT-0058.</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
@@ -1281,11 +1281,11 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>States, on the PTO liability page, a balance of 62.62 hours for Sora Jackson, TRT-0002.</t>
+          <t>States, in BambooHR, the PTO 5 Plus Years policy for Samuel Burkenham, TRT-0071.</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
@@ -1299,11 +1299,11 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>States, on the PTO liability page, a balance of 22.87 hours for Michael Labeson, TRT-0001.</t>
+          <t>States, in BambooHR, the PTO 2 to 5 Years policy for Wren Takahashi-Bell, TRT-0079.</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
@@ -1317,7 +1317,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>States, in BambooHR, the PTO 2 to 5 Years policy for Oren Kastellanos, TRT-0043.</t>
+          <t>States, in BambooHR, the PTO 2 to 5 Years policy for Desmond Achterberg, TRT-0083.</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
@@ -1335,7 +1335,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>States, in BambooHR, the PTO 2 to 5 Years policy for Priyamvada Raghunath, TRT-0051.</t>
+          <t>States, in BambooHR, for the 44 employees whose loaded policy is the tier's at 08/31/2026, the PTO Under 2 Years policy for TRT-0096, TRT-0099, TRT-0102, TRT-0105, TRT-0108, TRT-0110, TRT-0113, TRT-0119, TRT-0122, TRT-0128, TRT-0131, TRT-0135, TRT-0141, TRT-0150, TRT-0154, TRT-0156, the PTO 2 to 5 Years policy for TRT-0012, TRT-0014, TRT-0021, TRT-0023, TRT-0027, TRT-0029, TRT-0031, TRT-0034, TRT-0040, TRT-0045, TRT-0047, TRT-0052, TRT-0055, TRT-0062, TRT-0066, TRT-0069, TRT-0074, TRT-0076, TRT-0086, TRT-0088, TRT-0091, TRT-0093, TRT-0117, the PTO 5 Plus Years policy for TRT-0001, TRT-0002, TRT-0005, TRT-0009, TRT-0018.</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
@@ -1353,7 +1353,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>States, in BambooHR, the PTO 2 to 5 Years policy for Callum Oyelaran, TRT-0058.</t>
+          <t>States, in BambooHR, a PTO balance of 64.62 hours for Mikelle Hosana, TRT-0005.</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>States, in BambooHR, the PTO 5 Plus Years policy for Samuel Burkenham, TRT-0071.</t>
+          <t>States, in BambooHR, a PTO balance of 34.46 hours for Oren Kastellanos, TRT-0043.</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>States, in BambooHR, the PTO 2 to 5 Years policy for Wren Takahashi-Bell, TRT-0079.</t>
+          <t>States, in BambooHR, a PTO balance of 51.87 hours for Samuel Burkenham, TRT-0071.</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>States, in BambooHR, the PTO 2 to 5 Years policy for Desmond Achterberg, TRT-0083.</t>
+          <t>States, in BambooHR, a PTO balance of 60.00 hours for Marisela Thornbury, TRT-0018.</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
@@ -1425,7 +1425,7 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>States, in BambooHR, for the 44 employees whose loaded policy is the tier's at 08/31/2026, the PTO Under 2 Years policy for TRT-0096, TRT-0099, TRT-0102, TRT-0105, TRT-0108, TRT-0110, TRT-0113, TRT-0119, TRT-0122, TRT-0128, TRT-0131, TRT-0135, TRT-0141, TRT-0150, TRT-0154, TRT-0156, the PTO 2 to 5 Years policy for TRT-0012, TRT-0014, TRT-0021, TRT-0023, TRT-0027, TRT-0029, TRT-0031, TRT-0034, TRT-0040, TRT-0045, TRT-0047, TRT-0052, TRT-0055, TRT-0062, TRT-0066, TRT-0069, TRT-0074, TRT-0076, TRT-0086, TRT-0088, TRT-0091, TRT-0093, TRT-0117, the PTO 5 Plus Years policy for TRT-0001, TRT-0002, TRT-0005, TRT-0009, TRT-0018.</t>
+          <t>States, in BambooHR, a PTO balance of 29.60 hours for Beatriz Quintanilla, TRT-0141.</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
@@ -1443,7 +1443,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>States, in BambooHR, a PTO balance of 64.62 hours for Mikelle Hosana, TRT-0005.</t>
+          <t>States, in BambooHR, a PTO balance of 64.62 hours for Krystale Jumawan, TRT-0009.</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
@@ -1461,7 +1461,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>States, in BambooHR, a PTO balance of 34.46 hours for Oren Kastellanos, TRT-0043.</t>
+          <t>States, in BambooHR, a PTO balance of 18.46 hours for Jessica Ko, TRT-0012.</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
@@ -1479,7 +1479,7 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>States, in BambooHR, a PTO balance of 51.87 hours for Samuel Burkenham, TRT-0071.</t>
+          <t>States, in BambooHR, a PTO balance of 58.46 hours for Rohan Iyer, TRT-0014.</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
@@ -1497,7 +1497,7 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>States, in BambooHR, a PTO balance of 60.00 hours for Marisela Thornbury, TRT-0018.</t>
+          <t>States, in BambooHR, a PTO balance of 42.46 hours for Edith Bustamante, TRT-0021.</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
@@ -1515,7 +1515,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>States, in BambooHR, a PTO balance of 29.60 hours for Beatriz Quintanilla, TRT-0141.</t>
+          <t>States, in BambooHR, a PTO balance of 58.46 hours for Maeve Oyinlola, TRT-0023.</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
@@ -1533,7 +1533,7 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>States, in BambooHR, for the 33 employees whose loaded balance is the 08/31/2026 figure, a PTO balance of 22.87 hours for TRT-0001, 62.62 for TRT-0002, 26.71 for TRT-0027, 30.96 for TRT-0034, 7.96 for TRT-0045, 5.46 for TRT-0047, 4.46 for TRT-0052, 15.96 for TRT-0055, 21.21 for TRT-0062, 27.96 for TRT-0066, 46.21 for TRT-0069, 44.21 for TRT-0074, 35.21 for TRT-0076, 51.96 for TRT-0086, 13.21 for TRT-0088, 25.71 for TRT-0091, 20.21 for TRT-0093, 20.56 for TRT-0096, 37.06 for TRT-0099, 24.31 for TRT-0102, 15.81 for TRT-0105, 41.31 for TRT-0108, 23.81 for TRT-0110, 26.56 for TRT-0113, 8.46 for TRT-0117, 22.06 for TRT-0119, 31.31 for TRT-0122, 20.06 for TRT-0128, 4.31 for TRT-0131, 49.31 for TRT-0135, 12.31 for TRT-0150, 3.08 for TRT-0154, 0.00 for TRT-0156.</t>
+          <t>States, in BambooHR, a PTO balance of 50.46 hours for Emeka Thorsen, TRT-0029.</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
@@ -1551,7 +1551,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>States, in BambooHR, a PTO balance of 6.15 hours for Simone Okonkwo, TRT-0153.</t>
+          <t>States, in BambooHR, a PTO balance of 26.46 hours for Zephyr Adebayo, TRT-0031.</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
@@ -1569,7 +1569,7 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>States, in BambooHR, a PTO balance of 3.08 hours for Rafael Ibarra, TRT-0155.</t>
+          <t>States, in BambooHR, a PTO balance of 58.46 hours for Ilse Van der Kolk, TRT-0040.</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
@@ -1587,7 +1587,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>States, in BambooHR, the PTO Under 2 Years policy for Simone Okonkwo, TRT-0153.</t>
+          <t>States, in BambooHR, a PTO balance of 6.71 hours for Priyamvada Raghunath, TRT-0051.</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
@@ -1605,7 +1605,7 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>States, in BambooHR, the PTO Under 2 Years policy for Rafael Ibarra, TRT-0155.</t>
+          <t>States, in BambooHR, a PTO balance of 40.96 hours for Callum Oyelaran, TRT-0058.</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
@@ -1618,66 +1618,192 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="n"/>
-      <c r="B50" s="2" t="n"/>
-      <c r="C50" s="2" t="n"/>
-      <c r="D50" s="2" t="n"/>
+      <c r="A50" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>States, in BambooHR, a PTO balance of 24.96 hours for Wren Takahashi-Bell, TRT-0079.</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="inlineStr">
+      <c r="A51" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>States, in BambooHR, a PTO balance of 18.71 hours for Desmond Achterberg, TRT-0083.</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>States, in BambooHR, for the 33 employees whose loaded balance is the 08/31/2026 figure, a PTO balance of 22.87 hours for TRT-0001, 62.62 for TRT-0002, 26.71 for TRT-0027, 30.96 for TRT-0034, 7.96 for TRT-0045, 5.46 for TRT-0047, 4.46 for TRT-0052, 15.96 for TRT-0055, 21.21 for TRT-0062, 27.96 for TRT-0066, 46.21 for TRT-0069, 44.21 for TRT-0074, 35.21 for TRT-0076, 51.96 for TRT-0086, 13.21 for TRT-0088, 25.71 for TRT-0091, 20.21 for TRT-0093, 20.56 for TRT-0096, 37.06 for TRT-0099, 24.31 for TRT-0102, 15.81 for TRT-0105, 41.31 for TRT-0108, 23.81 for TRT-0110, 26.56 for TRT-0113, 8.46 for TRT-0117, 22.06 for TRT-0119, 31.31 for TRT-0122, 20.06 for TRT-0128, 4.31 for TRT-0131, 49.31 for TRT-0135, 12.31 for TRT-0150, 3.08 for TRT-0154, 0.00 for TRT-0156.</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>States, in BambooHR, a PTO balance of 6.15 hours for Simone Okonkwo, TRT-0153.</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>States, in BambooHR, a PTO balance of 3.08 hours for Rafael Ibarra, TRT-0155.</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>States, in BambooHR, the PTO Under 2 Years policy for Simone Okonkwo, TRT-0153.</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>States, in BambooHR, the PTO Under 2 Years policy for Rafael Ibarra, TRT-0155.</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="n"/>
+      <c r="B57" s="2" t="n"/>
+      <c r="C57" s="2" t="n"/>
+      <c r="D57" s="2" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
         <is>
           <t>The gate grades every rule across the whole group at once. It reads the total of all 52 liabilities, the one number all 364 cells feed, and it matches the schedule's only if every entry is right.</t>
         </is>
       </c>
-      <c r="C51" s="2" t="n"/>
-      <c r="D51" s="2" t="n"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
+      <c r="C58" s="2" t="n"/>
+      <c r="D58" s="2" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>Rows 15 to 22 and 28 to 31 each test one rule on one employee that rule alone moves. One wrong cell fails a rule once and never twice.</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="n"/>
-      <c r="D52" s="2" t="n"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>Rows 15 to 26 each test one rule on one employee that rule alone moves. One wrong cell fails a rule once and never twice.</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="n"/>
+      <c r="D59" s="2" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>Rows 23 to 27 each test one place the world breaks the definition of a current employee, the contractors and the four ended, and rows 28 to 29 the two unloaded hires. Row 2 tests the set as a whole.</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="n"/>
-      <c r="D53" s="2" t="n"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>Row 2 tests the population as a whole, the 52 present and no other, so the four contractors, the four ended records and the two unloaded hires each fail it. Rows 23 to 24 test the two unloaded hires on the page.</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="n"/>
+      <c r="D60" s="2" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>Rows 32 to 48 test BambooHR. One policy for each of the six records the schedule moves, one balance for each of five rules mirrored there, a balance and a policy for each of the two records created, and two rows over the 44 policies and 33 balances the schedule leaves as loaded.</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="n"/>
-      <c r="D54" s="2" t="n"/>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>Rows 27 to 55 test BambooHR. One policy for each of the six records the schedule moves, one balance for each of the 17 it moves, a balance and a policy for each of the two records created, and two rows over the 44 policies and 33 balances the schedule leaves as loaded.</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="n"/>
+      <c r="D61" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
